--- a/PRIZEPICKS_HITTER_AI_V4_TOP30_2026_07_17.xlsx
+++ b/PRIZEPICKS_HITTER_AI_V4_TOP30_2026_07_17.xlsx
@@ -1986,16 +1986,16 @@
         <v>83</v>
       </c>
       <c r="AC2" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="AD2" s="5" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="AE2" s="5" t="n">
-        <v>67.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="AF2" s="5" t="n">
-        <v>66.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="AG2" s="5" t="n">
         <v>63</v>
@@ -2004,10 +2004,10 @@
         <v>62.5</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
       <c r="AJ2" s="7" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="AK2" s="7" t="n">
         <v>48</v>
@@ -2022,13 +2022,13 @@
         <v>43.3</v>
       </c>
       <c r="AO2" s="8" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="AP2" s="8" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="AQ2" s="8" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="AR2" s="8" t="n">
         <v>33.3</v>
@@ -2037,16 +2037,16 @@
         <v>33.3</v>
       </c>
       <c r="AT2" s="8" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="AU2" s="8" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="AV2" s="8" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="AW2" s="8" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="AX2" s="8" t="n">
         <v>25.1</v>
@@ -2055,7 +2055,7 @@
         <v>25.1</v>
       </c>
       <c r="AZ2" s="3" t="n">
-        <v>279.62</v>
+        <v>279.61</v>
       </c>
       <c r="BA2" s="4" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>1.1096</v>
       </c>
       <c r="ES2" s="3" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="ET2" s="4" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>4.42</v>
       </c>
       <c r="FM2" s="3" t="n">
-        <v>15.61</v>
+        <v>15.62</v>
       </c>
       <c r="FN2" s="3" t="n">
         <v>21.21</v>
@@ -2463,7 +2463,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="FT2" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="FU2" s="3" t="n">
         <v>76</v>
@@ -2472,16 +2472,16 @@
         <v>76</v>
       </c>
       <c r="FW2" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="FX2" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="FY2" s="3" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
       <c r="FZ2" s="3" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
       <c r="GA2" s="3" t="n">
         <v>59.5</v>
@@ -2490,10 +2490,10 @@
         <v>59.5</v>
       </c>
       <c r="GC2" s="3" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="GD2" s="3" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="GE2" s="3" t="n">
         <v>48</v>
@@ -2508,13 +2508,13 @@
         <v>43.3</v>
       </c>
       <c r="GI2" s="3" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="GJ2" s="3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="GK2" s="3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="GL2" s="3" t="n">
         <v>33.3</v>
@@ -2523,16 +2523,16 @@
         <v>33.3</v>
       </c>
       <c r="GN2" s="3" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="GO2" s="3" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="GP2" s="3" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="GQ2" s="3" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="GR2" s="3" t="n">
         <v>25.1</v>
@@ -2544,7 +2544,7 @@
         <v>4.2</v>
       </c>
       <c r="GU2" s="3" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="GV2" s="3" t="n">
         <v>7.5</v>
@@ -2668,13 +2668,13 @@
         <v>10.78</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>10.73</v>
+        <v>10.74</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>10.73</v>
+        <v>10.74</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>9.34</v>
+        <v>9.35</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>7.5</v>
@@ -2734,43 +2734,43 @@
         <v>82.5</v>
       </c>
       <c r="AE3" s="5" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="AF3" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="AG3" s="5" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="AH3" s="5" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="AI3" s="5" t="n">
-        <v>64.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="AJ3" s="6" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="AK3" s="7" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="AL3" s="7" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="AM3" s="7" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="AN3" s="7" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="AO3" s="7" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="AP3" s="8" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="AQ3" s="8" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="AR3" s="8" t="n">
         <v>35.3</v>
@@ -2779,16 +2779,16 @@
         <v>35.3</v>
       </c>
       <c r="AT3" s="8" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="AU3" s="8" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="AV3" s="8" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="AW3" s="8" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="AX3" s="8" t="n">
         <v>23.1</v>
@@ -2797,7 +2797,7 @@
         <v>23.1</v>
       </c>
       <c r="AZ3" s="3" t="n">
-        <v>266.27</v>
+        <v>266.45</v>
       </c>
       <c r="BA3" s="4" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="BB3" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.5 | 64.4% | Edge +3.2</t>
+          <t>MORE 7.5 | 64.5% | Edge +3.2</t>
         </is>
       </c>
       <c r="BC3" s="4" t="inlineStr">
@@ -2818,13 +2818,13 @@
         <v>7.5</v>
       </c>
       <c r="BE3" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="BF3" s="3" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="BG3" s="3" t="n">
-        <v>28.8</v>
+        <v>29</v>
       </c>
       <c r="BH3" s="4" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>14.95</v>
       </c>
       <c r="FN3" s="3" t="n">
-        <v>20.55</v>
+        <v>20.56</v>
       </c>
       <c r="FO3" s="3" t="n">
         <v>4.84</v>
@@ -3211,52 +3211,52 @@
         <v>90.3</v>
       </c>
       <c r="FV3" s="3" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="FW3" s="3" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="FX3" s="3" t="n">
         <v>77.5</v>
       </c>
       <c r="FY3" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="FZ3" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="GA3" s="3" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="GB3" s="3" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="GC3" s="3" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="GD3" s="3" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="GE3" s="3" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="GF3" s="3" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="GG3" s="3" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="GH3" s="3" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="GI3" s="3" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="GJ3" s="3" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="GK3" s="3" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="GL3" s="3" t="n">
         <v>35.3</v>
@@ -3265,16 +3265,16 @@
         <v>35.3</v>
       </c>
       <c r="GN3" s="3" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="GO3" s="3" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="GP3" s="3" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="GQ3" s="3" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="GR3" s="3" t="n">
         <v>23.1</v>
@@ -3292,10 +3292,10 @@
         <v>3.6</v>
       </c>
       <c r="GW3" s="3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="GX3" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="GY3" s="3" t="n">
         <v>5</v>
@@ -3410,13 +3410,13 @@
         <v>11.38</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10.2</v>
+        <v>10.18</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>10.2</v>
+        <v>10.18</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>8.789999999999999</v>
@@ -3425,13 +3425,13 @@
         <v>7.86</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.73</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>7.86</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.901</v>
+        <v>0.902</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>12.6</v>
@@ -3482,49 +3482,49 @@
         <v>64.8</v>
       </c>
       <c r="AG4" s="5" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="AH4" s="5" t="n">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="AJ4" s="7" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="AK4" s="7" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="AL4" s="7" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="AM4" s="7" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="AN4" s="7" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="AO4" s="8" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="AP4" s="8" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="AQ4" s="8" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="AR4" s="8" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="AS4" s="8" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="AT4" s="8" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="AU4" s="8" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="AV4" s="8" t="n">
         <v>27.3</v>
@@ -3539,7 +3539,7 @@
         <v>22.4</v>
       </c>
       <c r="AZ4" s="3" t="n">
-        <v>263.07</v>
+        <v>262.76</v>
       </c>
       <c r="BA4" s="4" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="BB4" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.0 | 60.3% | Edge +3.2</t>
+          <t>MORE 7.0 | 60.2% | Edge +3.2</t>
         </is>
       </c>
       <c r="BC4" s="4" t="inlineStr">
@@ -3560,13 +3560,13 @@
         <v>7</v>
       </c>
       <c r="BE4" s="3" t="n">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
       <c r="BF4" s="3" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BG4" s="3" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="BH4" s="4" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         <v>3.71</v>
       </c>
       <c r="FM4" s="3" t="n">
-        <v>15.42</v>
+        <v>15.43</v>
       </c>
       <c r="FN4" s="3" t="n">
-        <v>20.83</v>
+        <v>20.84</v>
       </c>
       <c r="FO4" s="3" t="n">
         <v>4.75</v>
@@ -3968,49 +3968,49 @@
         <v>60.8</v>
       </c>
       <c r="GA4" s="3" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="GB4" s="3" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="GC4" s="3" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="GD4" s="3" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="GE4" s="3" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="GF4" s="3" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="GG4" s="3" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="GH4" s="3" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="GI4" s="3" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="GJ4" s="3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="GK4" s="3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="GL4" s="3" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="GM4" s="3" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="GN4" s="3" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="GO4" s="3" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="GP4" s="3" t="n">
         <v>27.3</v>
@@ -4120,168 +4120,168 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>LAD @ NYY</t>
+          <t>STL @ ARI</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>11.03</v>
+        <v>11.78</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>9.98</v>
+        <v>9.94</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>9.98</v>
+        <v>9.94</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>7.51</v>
+        <v>7.66</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>8.26</v>
+        <v>7.12</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>7.49</v>
+        <v>6.72</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>9.02</v>
+        <v>8.68</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>7.49</v>
+        <v>6.72</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.83</v>
+        <v>0.774</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>15.8</v>
+        <v>12.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>14.2</v>
+        <v>12</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>10.87</v>
+        <v>12.07</v>
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t>12|10|16|38|3</t>
+          <t>14|5|5|18|19</t>
         </is>
       </c>
       <c r="W5" s="4" t="inlineStr">
         <is>
-          <t>12|10|16|38|3|24|14|3|4|18</t>
+          <t>14|5|5|18|19|8|16|4|22|9</t>
         </is>
       </c>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>12|10|16|38|3|24|14|3|4|18|7|14|0|0|0</t>
+          <t>14|5|5|18|19|8|16|4|22|9|15|27|10|2|7</t>
         </is>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>91.7</v>
+        <v>92.3</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>91.7</v>
+        <v>92.3</v>
       </c>
       <c r="AA5" s="5" t="n">
-        <v>85.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="AB5" s="5" t="n">
-        <v>84.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>76.8</v>
+        <v>86.8</v>
       </c>
       <c r="AD5" s="5" t="n">
-        <v>75.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AE5" s="5" t="n">
-        <v>70.5</v>
+        <v>73.7</v>
       </c>
       <c r="AF5" s="5" t="n">
-        <v>61.3</v>
+        <v>73.2</v>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="AH5" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="AI5" s="7" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="AJ5" s="7" t="n">
-        <v>49.1</v>
+        <v>63.1</v>
+      </c>
+      <c r="AH5" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AI5" s="5" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="AJ5" s="6" t="n">
+        <v>50.5</v>
       </c>
       <c r="AK5" s="7" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="AL5" s="7" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="AM5" s="7" t="n">
-        <v>40.9</v>
+        <v>41.8</v>
       </c>
       <c r="AN5" s="8" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
       <c r="AO5" s="8" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
       <c r="AP5" s="8" t="n">
-        <v>36</v>
+        <v>35.3</v>
       </c>
       <c r="AQ5" s="8" t="n">
-        <v>36</v>
+        <v>35.3</v>
       </c>
       <c r="AR5" s="8" t="n">
-        <v>34</v>
+        <v>32.4</v>
       </c>
       <c r="AS5" s="8" t="n">
-        <v>32.9</v>
+        <v>30.8</v>
       </c>
       <c r="AT5" s="8" t="n">
-        <v>32.9</v>
+        <v>30.8</v>
       </c>
       <c r="AU5" s="8" t="n">
-        <v>28.3</v>
+        <v>25.9</v>
       </c>
       <c r="AV5" s="8" t="n">
-        <v>28.3</v>
+        <v>24.9</v>
       </c>
       <c r="AW5" s="8" t="n">
-        <v>27.6</v>
+        <v>24.9</v>
       </c>
       <c r="AX5" s="8" t="n">
-        <v>22.8</v>
+        <v>21.3</v>
       </c>
       <c r="AY5" s="8" t="n">
-        <v>22.8</v>
+        <v>19.1</v>
       </c>
       <c r="AZ5" s="3" t="n">
-        <v>258.04</v>
+        <v>258.25</v>
       </c>
       <c r="BA5" s="4" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="BB5" s="9" t="inlineStr">
         <is>
-          <t>MORE 6.5 | 60.8% | Edge +3.5</t>
+          <t>MORE 7.5 | 58.5% | Edge +2.4</t>
         </is>
       </c>
       <c r="BC5" s="4" t="inlineStr">
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="BD5" s="3" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="BE5" s="3" t="n">
-        <v>60.8</v>
+        <v>58.5</v>
       </c>
       <c r="BF5" s="3" t="n">
-        <v>3.48</v>
+        <v>2.44</v>
       </c>
       <c r="BG5" s="3" t="n">
-        <v>21.6</v>
+        <v>17</v>
       </c>
       <c r="BH5" s="4" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ5" s="4" t="inlineStr">
         <is>
@@ -4325,24 +4325,24 @@
       </c>
       <c r="BK5" s="4" t="n"/>
       <c r="BL5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM5" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN5" s="4" t="inlineStr">
         <is>
-          <t>2-2-2-2-2-3-2</t>
+          <t>3-4-3-4-3-3-4</t>
         </is>
       </c>
       <c r="BO5" s="3" t="n">
-        <v>85.7</v>
+        <v>57.1</v>
       </c>
       <c r="BP5" s="3" t="n">
         <v>97</v>
       </c>
       <c r="BQ5" s="3" t="n">
-        <v>5.02</v>
+        <v>4.92</v>
       </c>
       <c r="BR5" s="4" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="BU5" s="4" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Merrill Kelly</t>
         </is>
       </c>
       <c r="BV5" s="4" t="inlineStr">
@@ -4366,124 +4366,116 @@
         </is>
       </c>
       <c r="BW5" s="3" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="BX5" s="3" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="BY5" s="3" t="n">
-        <v>0.2188</v>
+        <v>0.2506</v>
       </c>
       <c r="BZ5" s="3" t="n">
-        <v>0.054</v>
+        <v>0.0487</v>
       </c>
       <c r="CA5" s="3" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0925</v>
       </c>
       <c r="CB5" s="3" t="n">
-        <v>3.55</v>
+        <v>4.21</v>
       </c>
       <c r="CC5" s="3" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="CD5" s="3" t="n">
-        <v>0.1942</v>
+        <v>0.2245</v>
       </c>
       <c r="CE5" s="3" t="n">
-        <v>0.0298</v>
+        <v>0.0325</v>
       </c>
       <c r="CF5" s="4" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="CG5" s="3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="CH5" s="3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="CI5" s="3" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="CJ5" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="CK5" s="3" t="n">
-        <v>326</v>
-      </c>
-      <c r="CL5" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="CI5" s="4" t="n"/>
+      <c r="CJ5" s="4" t="n"/>
+      <c r="CK5" s="4" t="n"/>
+      <c r="CL5" s="4" t="n"/>
       <c r="CM5" s="4" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>Indoor/retractable neutral</t>
         </is>
       </c>
       <c r="CN5" s="3" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="CO5" s="3" t="n">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="CP5" s="3" t="n">
-        <v>0.279</v>
+        <v>0.294</v>
       </c>
       <c r="CQ5" s="3" t="n">
-        <v>0.372</v>
+        <v>0.354</v>
       </c>
       <c r="CR5" s="3" t="n">
-        <v>0.599</v>
+        <v>0.532</v>
       </c>
       <c r="CS5" s="3" t="n">
-        <v>0.971</v>
+        <v>0.886</v>
       </c>
       <c r="CT5" s="3" t="n">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="CU5" s="3" t="n">
-        <v>1.041</v>
+        <v>0.863</v>
       </c>
       <c r="CV5" s="3" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="CW5" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="CX5" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CY5" s="3" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="CZ5" s="3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="DA5" s="3" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="DB5" s="3" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="DC5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="DD5" s="3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="DE5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Washington Nationals: 12 FS|2026-07-11 @ Washington Nationals: 10 FS|2026-07-10 @ Washington Nationals: 16 FS|2026-07-09 @ Tampa Bay Rays: 38 FS|2026-07-08 @ Tampa Bay Rays: 3 FS</t>
+          <t>2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS|2026-07-08 vs Milwaukee Brewers: 19 FS</t>
         </is>
       </c>
       <c r="DF5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Washington Nationals: 12 FS|2026-07-11 @ Washington Nationals: 10 FS|2026-07-10 @ Washington Nationals: 16 FS|2026-07-09 @ Tampa Bay Rays: 38 FS|2026-07-08 @ Tampa Bay Rays: 3 FS|2026-07-07 @ Tampa Bay Rays: 24 FS|2026-07-06 @ Tampa Bay Rays: 14 FS|2026-07-05 vs Minnesota Twins: 3 FS|2026-07-04 vs Minnesota Twins: 4 FS|2026-07-03 vs Minnesota Twins: 18 FS</t>
+          <t>2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS|2026-07-08 vs Milwaukee Brewers: 19 FS|2026-07-07 vs Milwaukee Brewers: 8 FS|2026-07-07 vs Milwaukee Brewers: 16 FS|2026-07-06 vs Milwaukee Brewers: 4 FS|2026-07-05 @ Chicago Cubs: 22 FS|2026-07-04 @ Chicago Cubs: 9 FS</t>
         </is>
       </c>
       <c r="DG5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Washington Nationals: 12 FS|2026-07-11 @ Washington Nationals: 10 FS|2026-07-10 @ Washington Nationals: 16 FS|2026-07-09 @ Tampa Bay Rays: 38 FS|2026-07-08 @ Tampa Bay Rays: 3 FS|2026-07-07 @ Tampa Bay Rays: 24 FS|2026-07-06 @ Tampa Bay Rays: 14 FS|2026-07-05 vs Minnesota Twins: 3 FS|2026-07-04 vs Minnesota Twins: 4 FS|2026-07-03 vs Minnesota Twins: 18 FS|2026-07-01 vs Detroit Tigers: 7 FS|2026-06-30 vs Detroit Tigers: 14 FS|2026-06-29 vs Detroit Tigers: 0 FS|2026-06-28 @ Boston Red Sox: 0 FS|2026-06-27 @ Boston Red Sox: 0 FS</t>
+          <t>2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS|2026-07-08 vs Milwaukee Brewers: 19 FS|2026-07-07 vs Milwaukee Brewers: 8 FS|2026-07-07 vs Milwaukee Brewers: 16 FS|2026-07-06 vs Milwaukee Brewers: 4 FS|2026-07-05 @ Chicago Cubs: 22 FS|2026-07-04 @ Chicago Cubs: 9 FS|2026-07-03 @ Chicago Cubs: 15 FS|2026-07-02 @ Atlanta Braves: 27 FS|2026-07-01 @ Atlanta Braves: 10 FS|2026-06-30 @ Atlanta Braves: 2 FS|2026-06-27 vs Miami Marlins: 7 FS</t>
         </is>
       </c>
       <c r="DH5" s="3" t="n">
@@ -4493,10 +4485,10 @@
         <v>30</v>
       </c>
       <c r="DJ5" s="3" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="DK5" s="3" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="DL5" s="4" t="inlineStr">
         <is>
@@ -4504,54 +4496,54 @@
         </is>
       </c>
       <c r="DM5" s="3" t="n">
-        <v>16.71</v>
+        <v>12.14</v>
       </c>
       <c r="DN5" s="3" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="DO5" s="3" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="DP5" s="4" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="DQ5" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="DR5" s="3" t="n">
+        <v>3.053</v>
+      </c>
+      <c r="DS5" s="3" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="DT5" s="3" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="DU5" s="3" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="DV5" s="3" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="DW5" s="3" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="DX5" s="3" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="DY5" s="3" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="DZ5" s="3" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="EA5" s="3" t="n">
         <v>11.64</v>
       </c>
-      <c r="DO5" s="3" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="DP5" s="4" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="DQ5" s="3" t="n">
-        <v>9.07</v>
-      </c>
-      <c r="DR5" s="3" t="n">
-        <v>2.717</v>
-      </c>
-      <c r="DS5" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DT5" s="3" t="n">
-        <v>0.1333</v>
-      </c>
-      <c r="DU5" s="3" t="n">
-        <v>0.1167</v>
-      </c>
-      <c r="DV5" s="3" t="n">
-        <v>0.1333</v>
-      </c>
-      <c r="DW5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX5" s="3" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="DY5" s="3" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="DZ5" s="3" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="EA5" s="3" t="n">
-        <v>11.71</v>
-      </c>
       <c r="EB5" s="3" t="n">
-        <v>10.45</v>
+        <v>10.63</v>
       </c>
       <c r="EC5" s="3" t="n">
         <v>28</v>
@@ -4569,25 +4561,25 @@
         <v>20</v>
       </c>
       <c r="EH5" s="3" t="n">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="EI5" s="3" t="n">
-        <v>85.04000000000001</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="EJ5" s="3" t="n">
-        <v>28.62</v>
+        <v>30.45</v>
       </c>
       <c r="EK5" s="3" t="n">
-        <v>3.62</v>
+        <v>2.47</v>
       </c>
       <c r="EL5" s="3" t="n">
-        <v>31.52</v>
+        <v>28.4</v>
       </c>
       <c r="EM5" s="3" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="EN5" s="3" t="n">
-        <v>0.9863</v>
+        <v>1.0232</v>
       </c>
       <c r="EO5" s="3" t="n">
         <v>1</v>
@@ -4599,10 +4591,10 @@
         <v>1</v>
       </c>
       <c r="ER5" s="3" t="n">
-        <v>1.0379</v>
+        <v>1.0564</v>
       </c>
       <c r="ES5" s="3" t="n">
-        <v>361</v>
+        <v>472</v>
       </c>
       <c r="ET5" s="4" t="inlineStr">
         <is>
@@ -4610,43 +4602,43 @@
         </is>
       </c>
       <c r="EU5" s="3" t="n">
-        <v>0.1212</v>
+        <v>0.1694</v>
       </c>
       <c r="EV5" s="3" t="n">
-        <v>0.0379</v>
+        <v>0.0541</v>
       </c>
       <c r="EW5" s="3" t="n">
-        <v>0.0056</v>
+        <v>0.003</v>
       </c>
       <c r="EX5" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0635</v>
       </c>
       <c r="EY5" s="3" t="n">
-        <v>0.1149</v>
+        <v>0.0864</v>
       </c>
       <c r="EZ5" s="3" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0106</v>
       </c>
       <c r="FA5" s="3" t="n">
-        <v>0.2335</v>
+        <v>0.2138</v>
       </c>
       <c r="FB5" s="3" t="n">
-        <v>0.45</v>
+        <v>0.4888</v>
       </c>
       <c r="FC5" s="3" t="n">
-        <v>0.3357</v>
+        <v>0.203</v>
       </c>
       <c r="FD5" s="3" t="n">
-        <v>0.2143</v>
+        <v>0.3082</v>
       </c>
       <c r="FE5" s="3" t="n">
-        <v>0.1342</v>
+        <v>0.1483</v>
       </c>
       <c r="FF5" s="3" t="n">
-        <v>0.1613</v>
+        <v>0.1864</v>
       </c>
       <c r="FG5" s="3" t="n">
-        <v>0.0086</v>
+        <v>0.019</v>
       </c>
       <c r="FH5" s="3" t="n">
         <v>1</v>
@@ -4658,19 +4650,19 @@
       </c>
       <c r="FJ5" s="4" t="n"/>
       <c r="FK5" s="3" t="n">
-        <v>7.49</v>
+        <v>6.72</v>
       </c>
       <c r="FL5" s="3" t="n">
-        <v>4.19</v>
+        <v>4.57</v>
       </c>
       <c r="FM5" s="3" t="n">
-        <v>14.98</v>
+        <v>13.86</v>
       </c>
       <c r="FN5" s="3" t="n">
-        <v>19.96</v>
+        <v>19.27</v>
       </c>
       <c r="FO5" s="3" t="n">
-        <v>4.67</v>
+        <v>4.39</v>
       </c>
       <c r="FP5" s="3" t="n">
         <v>0</v>
@@ -4686,100 +4678,100 @@
         </is>
       </c>
       <c r="FS5" s="3" t="n">
-        <v>86.2</v>
+        <v>87.2</v>
       </c>
       <c r="FT5" s="3" t="n">
-        <v>86.2</v>
+        <v>87.2</v>
       </c>
       <c r="FU5" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="FV5" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="FW5" s="3" t="n">
-        <v>70.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="FX5" s="3" t="n">
-        <v>70.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="FY5" s="3" t="n">
-        <v>66</v>
+        <v>69.2</v>
       </c>
       <c r="FZ5" s="3" t="n">
-        <v>57.3</v>
+        <v>69.2</v>
       </c>
       <c r="GA5" s="3" t="n">
-        <v>57.3</v>
+        <v>59.6</v>
       </c>
       <c r="GB5" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="GC5" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="GD5" s="3" t="n">
-        <v>48.1</v>
+        <v>49.5</v>
       </c>
       <c r="GE5" s="3" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="GF5" s="3" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="GG5" s="3" t="n">
-        <v>40.9</v>
+        <v>41.8</v>
       </c>
       <c r="GH5" s="3" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
       <c r="GI5" s="3" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
       <c r="GJ5" s="3" t="n">
-        <v>36</v>
+        <v>35.3</v>
       </c>
       <c r="GK5" s="3" t="n">
-        <v>36</v>
+        <v>35.3</v>
       </c>
       <c r="GL5" s="3" t="n">
-        <v>34</v>
+        <v>32.4</v>
       </c>
       <c r="GM5" s="3" t="n">
-        <v>32.9</v>
+        <v>30.8</v>
       </c>
       <c r="GN5" s="3" t="n">
-        <v>32.9</v>
+        <v>30.8</v>
       </c>
       <c r="GO5" s="3" t="n">
-        <v>28.3</v>
+        <v>25.9</v>
       </c>
       <c r="GP5" s="3" t="n">
-        <v>28.3</v>
+        <v>24.9</v>
       </c>
       <c r="GQ5" s="3" t="n">
-        <v>27.6</v>
+        <v>24.9</v>
       </c>
       <c r="GR5" s="3" t="n">
-        <v>22.8</v>
+        <v>21.3</v>
       </c>
       <c r="GS5" s="3" t="n">
-        <v>22.8</v>
+        <v>19.1</v>
       </c>
       <c r="GT5" s="3" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="GU5" s="3" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="GV5" s="3" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="GW5" s="3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="GX5" s="3" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="GY5" s="3" t="n">
         <v>5</v>
@@ -4862,168 +4854,168 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>STL @ ARI</t>
+          <t>LAD @ NYY</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>11.78</v>
+        <v>11.03</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>9.92</v>
+        <v>9.98</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>9.92</v>
+        <v>9.98</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>7.65</v>
+        <v>7.51</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>7.12</v>
+        <v>8.26</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>6.72</v>
+        <v>7.49</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>8.65</v>
+        <v>9.02</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>6.72</v>
+        <v>7.49</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.777</v>
+        <v>0.83</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>12.2</v>
+        <v>15.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>12</v>
+        <v>14.2</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>12.07</v>
+        <v>10.87</v>
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>14|5|5|18|19</t>
+          <t>12|10|16|38|3</t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>14|5|5|18|19|8|16|4|22|9</t>
+          <t>12|10|16|38|3|24|14|3|4|18</t>
         </is>
       </c>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>14|5|5|18|19|8|16|4|22|9|15|27|10|2|7</t>
+          <t>12|10|16|38|3|24|14|3|4|18|7|14|0|0|0</t>
         </is>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>92.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="Z6" s="5" t="n">
-        <v>92.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="AA6" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AB6" s="5" t="n">
-        <v>87.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>86.8</v>
+        <v>76.8</v>
       </c>
       <c r="AD6" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="AE6" s="5" t="n">
-        <v>73.8</v>
+        <v>70.5</v>
       </c>
       <c r="AF6" s="5" t="n">
-        <v>73.3</v>
+        <v>61.3</v>
       </c>
       <c r="AG6" s="5" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="AH6" s="5" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="AI6" s="5" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="AJ6" s="6" t="n">
-        <v>50.3</v>
+        <v>60.8</v>
+      </c>
+      <c r="AH6" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="AI6" s="7" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AJ6" s="7" t="n">
+        <v>49.1</v>
       </c>
       <c r="AK6" s="7" t="n">
-        <v>45.1</v>
+        <v>44.6</v>
       </c>
       <c r="AL6" s="7" t="n">
-        <v>45.1</v>
+        <v>44.6</v>
       </c>
       <c r="AM6" s="7" t="n">
-        <v>41.8</v>
+        <v>40.9</v>
       </c>
       <c r="AN6" s="8" t="n">
-        <v>37.6</v>
+        <v>37.9</v>
       </c>
       <c r="AO6" s="8" t="n">
-        <v>37.6</v>
+        <v>37.9</v>
       </c>
       <c r="AP6" s="8" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="AQ6" s="8" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="AR6" s="8" t="n">
-        <v>32.5</v>
+        <v>34</v>
       </c>
       <c r="AS6" s="8" t="n">
-        <v>30.9</v>
+        <v>32.9</v>
       </c>
       <c r="AT6" s="8" t="n">
-        <v>30.9</v>
+        <v>32.9</v>
       </c>
       <c r="AU6" s="8" t="n">
-        <v>25.9</v>
+        <v>28.3</v>
       </c>
       <c r="AV6" s="8" t="n">
-        <v>24.8</v>
+        <v>28.3</v>
       </c>
       <c r="AW6" s="8" t="n">
-        <v>24.8</v>
+        <v>27.6</v>
       </c>
       <c r="AX6" s="8" t="n">
-        <v>21.2</v>
+        <v>22.8</v>
       </c>
       <c r="AY6" s="8" t="n">
-        <v>19.1</v>
+        <v>22.8</v>
       </c>
       <c r="AZ6" s="3" t="n">
-        <v>257.93</v>
+        <v>258.04</v>
       </c>
       <c r="BA6" s="4" t="inlineStr">
         <is>
@@ -5032,7 +5024,7 @@
       </c>
       <c r="BB6" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.5 | 58.4% | Edge +2.4</t>
+          <t>MORE 6.5 | 60.8% | Edge +3.5</t>
         </is>
       </c>
       <c r="BC6" s="4" t="inlineStr">
@@ -5041,16 +5033,16 @@
         </is>
       </c>
       <c r="BD6" s="3" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="BE6" s="3" t="n">
-        <v>58.4</v>
+        <v>60.8</v>
       </c>
       <c r="BF6" s="3" t="n">
-        <v>2.42</v>
+        <v>3.48</v>
       </c>
       <c r="BG6" s="3" t="n">
-        <v>16.8</v>
+        <v>21.6</v>
       </c>
       <c r="BH6" s="4" t="inlineStr">
         <is>
@@ -5058,7 +5050,7 @@
         </is>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ6" s="4" t="inlineStr">
         <is>
@@ -5067,24 +5059,24 @@
       </c>
       <c r="BK6" s="4" t="n"/>
       <c r="BL6" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM6" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN6" s="4" t="inlineStr">
         <is>
-          <t>3-4-3-4-3-3-4</t>
+          <t>2-2-2-2-2-3-2</t>
         </is>
       </c>
       <c r="BO6" s="3" t="n">
-        <v>57.1</v>
+        <v>85.7</v>
       </c>
       <c r="BP6" s="3" t="n">
         <v>97</v>
       </c>
       <c r="BQ6" s="3" t="n">
-        <v>4.92</v>
+        <v>5.02</v>
       </c>
       <c r="BR6" s="4" t="inlineStr">
         <is>
@@ -5099,7 +5091,7 @@
       </c>
       <c r="BU6" s="4" t="inlineStr">
         <is>
-          <t>Merrill Kelly</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="BV6" s="4" t="inlineStr">
@@ -5108,116 +5100,124 @@
         </is>
       </c>
       <c r="BW6" s="3" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="BX6" s="3" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="BY6" s="3" t="n">
-        <v>0.2506</v>
+        <v>0.2188</v>
       </c>
       <c r="BZ6" s="3" t="n">
-        <v>0.0487</v>
+        <v>0.054</v>
       </c>
       <c r="CA6" s="3" t="n">
-        <v>0.0925</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="CB6" s="3" t="n">
-        <v>4.21</v>
+        <v>3.55</v>
       </c>
       <c r="CC6" s="3" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="CD6" s="3" t="n">
-        <v>0.2245</v>
+        <v>0.1942</v>
       </c>
       <c r="CE6" s="3" t="n">
-        <v>0.0325</v>
+        <v>0.0298</v>
       </c>
       <c r="CF6" s="4" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="CG6" s="3" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="CH6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI6" s="4" t="n"/>
-      <c r="CJ6" s="4" t="n"/>
-      <c r="CK6" s="4" t="n"/>
-      <c r="CL6" s="4" t="n"/>
+        <v>1.03</v>
+      </c>
+      <c r="CI6" s="3" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="CJ6" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="CK6" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="CL6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="CM6" s="4" t="inlineStr">
         <is>
-          <t>Indoor/retractable neutral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CN6" s="3" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="CO6" s="3" t="n">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="CP6" s="3" t="n">
-        <v>0.294</v>
+        <v>0.279</v>
       </c>
       <c r="CQ6" s="3" t="n">
-        <v>0.354</v>
+        <v>0.372</v>
       </c>
       <c r="CR6" s="3" t="n">
-        <v>0.532</v>
+        <v>0.599</v>
       </c>
       <c r="CS6" s="3" t="n">
-        <v>0.886</v>
+        <v>0.971</v>
       </c>
       <c r="CT6" s="3" t="n">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="CU6" s="3" t="n">
-        <v>0.863</v>
+        <v>1.041</v>
       </c>
       <c r="CV6" s="3" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="CW6" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CX6" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CY6" s="3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="CZ6" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="DA6" s="3" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="DB6" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="DC6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="DD6" s="3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="DE6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS|2026-07-08 vs Milwaukee Brewers: 19 FS</t>
+          <t>2026-07-12 @ Washington Nationals: 12 FS|2026-07-11 @ Washington Nationals: 10 FS|2026-07-10 @ Washington Nationals: 16 FS|2026-07-09 @ Tampa Bay Rays: 38 FS|2026-07-08 @ Tampa Bay Rays: 3 FS</t>
         </is>
       </c>
       <c r="DF6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS|2026-07-08 vs Milwaukee Brewers: 19 FS|2026-07-07 vs Milwaukee Brewers: 8 FS|2026-07-07 vs Milwaukee Brewers: 16 FS|2026-07-06 vs Milwaukee Brewers: 4 FS|2026-07-05 @ Chicago Cubs: 22 FS|2026-07-04 @ Chicago Cubs: 9 FS</t>
+          <t>2026-07-12 @ Washington Nationals: 12 FS|2026-07-11 @ Washington Nationals: 10 FS|2026-07-10 @ Washington Nationals: 16 FS|2026-07-09 @ Tampa Bay Rays: 38 FS|2026-07-08 @ Tampa Bay Rays: 3 FS|2026-07-07 @ Tampa Bay Rays: 24 FS|2026-07-06 @ Tampa Bay Rays: 14 FS|2026-07-05 vs Minnesota Twins: 3 FS|2026-07-04 vs Minnesota Twins: 4 FS|2026-07-03 vs Minnesota Twins: 18 FS</t>
         </is>
       </c>
       <c r="DG6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS|2026-07-08 vs Milwaukee Brewers: 19 FS|2026-07-07 vs Milwaukee Brewers: 8 FS|2026-07-07 vs Milwaukee Brewers: 16 FS|2026-07-06 vs Milwaukee Brewers: 4 FS|2026-07-05 @ Chicago Cubs: 22 FS|2026-07-04 @ Chicago Cubs: 9 FS|2026-07-03 @ Chicago Cubs: 15 FS|2026-07-02 @ Atlanta Braves: 27 FS|2026-07-01 @ Atlanta Braves: 10 FS|2026-06-30 @ Atlanta Braves: 2 FS|2026-06-27 vs Miami Marlins: 7 FS</t>
+          <t>2026-07-12 @ Washington Nationals: 12 FS|2026-07-11 @ Washington Nationals: 10 FS|2026-07-10 @ Washington Nationals: 16 FS|2026-07-09 @ Tampa Bay Rays: 38 FS|2026-07-08 @ Tampa Bay Rays: 3 FS|2026-07-07 @ Tampa Bay Rays: 24 FS|2026-07-06 @ Tampa Bay Rays: 14 FS|2026-07-05 vs Minnesota Twins: 3 FS|2026-07-04 vs Minnesota Twins: 4 FS|2026-07-03 vs Minnesota Twins: 18 FS|2026-07-01 vs Detroit Tigers: 7 FS|2026-06-30 vs Detroit Tigers: 14 FS|2026-06-29 vs Detroit Tigers: 0 FS|2026-06-28 @ Boston Red Sox: 0 FS|2026-06-27 @ Boston Red Sox: 0 FS</t>
         </is>
       </c>
       <c r="DH6" s="3" t="n">
@@ -5227,10 +5227,10 @@
         <v>30</v>
       </c>
       <c r="DJ6" s="3" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="DK6" s="3" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="DL6" s="4" t="inlineStr">
         <is>
@@ -5238,54 +5238,54 @@
         </is>
       </c>
       <c r="DM6" s="3" t="n">
-        <v>12.14</v>
+        <v>16.71</v>
       </c>
       <c r="DN6" s="3" t="n">
-        <v>12.43</v>
+        <v>11.64</v>
       </c>
       <c r="DO6" s="3" t="n">
-        <v>0.319</v>
+        <v>0.294</v>
       </c>
       <c r="DP6" s="4" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="DQ6" s="3" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="DR6" s="3" t="n">
-        <v>3.053</v>
+        <v>2.717</v>
       </c>
       <c r="DS6" s="3" t="n">
-        <v>0.2632</v>
+        <v>0.25</v>
       </c>
       <c r="DT6" s="3" t="n">
-        <v>0.1228</v>
+        <v>0.1333</v>
       </c>
       <c r="DU6" s="3" t="n">
-        <v>0.0702</v>
+        <v>0.1167</v>
       </c>
       <c r="DV6" s="3" t="n">
-        <v>0.1404</v>
+        <v>0.1333</v>
       </c>
       <c r="DW6" s="3" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="DX6" s="3" t="n">
-        <v>12.25</v>
+        <v>11.39</v>
       </c>
       <c r="DY6" s="3" t="n">
-        <v>11.43</v>
+        <v>10.37</v>
       </c>
       <c r="DZ6" s="3" t="n">
-        <v>12.68</v>
+        <v>11.08</v>
       </c>
       <c r="EA6" s="3" t="n">
-        <v>11.64</v>
+        <v>11.71</v>
       </c>
       <c r="EB6" s="3" t="n">
-        <v>10.63</v>
+        <v>10.45</v>
       </c>
       <c r="EC6" s="3" t="n">
         <v>28</v>
@@ -5303,25 +5303,25 @@
         <v>20</v>
       </c>
       <c r="EH6" s="3" t="n">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="EI6" s="3" t="n">
-        <v>86.54000000000001</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="EJ6" s="3" t="n">
-        <v>30.45</v>
+        <v>28.62</v>
       </c>
       <c r="EK6" s="3" t="n">
-        <v>2.47</v>
+        <v>3.62</v>
       </c>
       <c r="EL6" s="3" t="n">
-        <v>28.4</v>
+        <v>31.52</v>
       </c>
       <c r="EM6" s="3" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="EN6" s="3" t="n">
-        <v>1.0232</v>
+        <v>0.9863</v>
       </c>
       <c r="EO6" s="3" t="n">
         <v>1</v>
@@ -5333,10 +5333,10 @@
         <v>1</v>
       </c>
       <c r="ER6" s="3" t="n">
-        <v>1.0564</v>
+        <v>1.0379</v>
       </c>
       <c r="ES6" s="3" t="n">
-        <v>472</v>
+        <v>361</v>
       </c>
       <c r="ET6" s="4" t="inlineStr">
         <is>
@@ -5344,43 +5344,43 @@
         </is>
       </c>
       <c r="EU6" s="3" t="n">
-        <v>0.1694</v>
+        <v>0.1212</v>
       </c>
       <c r="EV6" s="3" t="n">
-        <v>0.0541</v>
+        <v>0.0379</v>
       </c>
       <c r="EW6" s="3" t="n">
-        <v>0.003</v>
+        <v>0.0056</v>
       </c>
       <c r="EX6" s="3" t="n">
-        <v>0.0635</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="EY6" s="3" t="n">
-        <v>0.0864</v>
+        <v>0.1149</v>
       </c>
       <c r="EZ6" s="3" t="n">
-        <v>0.0106</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="FA6" s="3" t="n">
-        <v>0.2138</v>
+        <v>0.2335</v>
       </c>
       <c r="FB6" s="3" t="n">
-        <v>0.4888</v>
+        <v>0.45</v>
       </c>
       <c r="FC6" s="3" t="n">
-        <v>0.203</v>
+        <v>0.3357</v>
       </c>
       <c r="FD6" s="3" t="n">
-        <v>0.3082</v>
+        <v>0.2143</v>
       </c>
       <c r="FE6" s="3" t="n">
-        <v>0.1483</v>
+        <v>0.1342</v>
       </c>
       <c r="FF6" s="3" t="n">
-        <v>0.1864</v>
+        <v>0.1613</v>
       </c>
       <c r="FG6" s="3" t="n">
-        <v>0.019</v>
+        <v>0.0086</v>
       </c>
       <c r="FH6" s="3" t="n">
         <v>1</v>
@@ -5392,19 +5392,19 @@
       </c>
       <c r="FJ6" s="4" t="n"/>
       <c r="FK6" s="3" t="n">
-        <v>6.72</v>
+        <v>7.49</v>
       </c>
       <c r="FL6" s="3" t="n">
-        <v>4.55</v>
+        <v>4.19</v>
       </c>
       <c r="FM6" s="3" t="n">
-        <v>13.87</v>
+        <v>14.98</v>
       </c>
       <c r="FN6" s="3" t="n">
-        <v>19.3</v>
+        <v>19.96</v>
       </c>
       <c r="FO6" s="3" t="n">
-        <v>4.39</v>
+        <v>4.67</v>
       </c>
       <c r="FP6" s="3" t="n">
         <v>0</v>
@@ -5420,100 +5420,100 @@
         </is>
       </c>
       <c r="FS6" s="3" t="n">
-        <v>87.3</v>
+        <v>86.2</v>
       </c>
       <c r="FT6" s="3" t="n">
-        <v>87.3</v>
+        <v>86.2</v>
       </c>
       <c r="FU6" s="3" t="n">
-        <v>87.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="FV6" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="FW6" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="FX6" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="FY6" s="3" t="n">
-        <v>69.3</v>
+        <v>66</v>
       </c>
       <c r="FZ6" s="3" t="n">
-        <v>69.3</v>
+        <v>57.3</v>
       </c>
       <c r="GA6" s="3" t="n">
-        <v>59.4</v>
+        <v>57.3</v>
       </c>
       <c r="GB6" s="3" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="GC6" s="3" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="GD6" s="3" t="n">
-        <v>49.3</v>
+        <v>48.1</v>
       </c>
       <c r="GE6" s="3" t="n">
-        <v>45.1</v>
+        <v>44.6</v>
       </c>
       <c r="GF6" s="3" t="n">
-        <v>45.1</v>
+        <v>44.6</v>
       </c>
       <c r="GG6" s="3" t="n">
-        <v>41.8</v>
+        <v>40.9</v>
       </c>
       <c r="GH6" s="3" t="n">
-        <v>37.6</v>
+        <v>37.9</v>
       </c>
       <c r="GI6" s="3" t="n">
-        <v>37.6</v>
+        <v>37.9</v>
       </c>
       <c r="GJ6" s="3" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="GK6" s="3" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="GL6" s="3" t="n">
-        <v>32.5</v>
+        <v>34</v>
       </c>
       <c r="GM6" s="3" t="n">
-        <v>30.9</v>
+        <v>32.9</v>
       </c>
       <c r="GN6" s="3" t="n">
-        <v>30.9</v>
+        <v>32.9</v>
       </c>
       <c r="GO6" s="3" t="n">
-        <v>25.9</v>
+        <v>28.3</v>
       </c>
       <c r="GP6" s="3" t="n">
-        <v>24.8</v>
+        <v>28.3</v>
       </c>
       <c r="GQ6" s="3" t="n">
-        <v>24.8</v>
+        <v>27.6</v>
       </c>
       <c r="GR6" s="3" t="n">
-        <v>21.2</v>
+        <v>22.8</v>
       </c>
       <c r="GS6" s="3" t="n">
-        <v>19.1</v>
+        <v>22.8</v>
       </c>
       <c r="GT6" s="3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="GU6" s="3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="GV6" s="3" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="GW6" s="3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="GX6" s="3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="GY6" s="3" t="n">
         <v>5</v>
@@ -5643,7 +5643,7 @@
         <v>7.57</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.33</v>
+        <v>8.34</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>7.57</v>
@@ -5691,7 +5691,7 @@
         <v>79.8</v>
       </c>
       <c r="AD7" s="5" t="n">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="AE7" s="5" t="n">
         <v>64.8</v>
@@ -5706,16 +5706,16 @@
         <v>60.6</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="AJ7" s="7" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="AK7" s="7" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="AL7" s="7" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="AM7" s="7" t="n">
         <v>41.6</v>
@@ -5757,7 +5757,7 @@
         <v>20.1</v>
       </c>
       <c r="AZ7" s="3" t="n">
-        <v>255</v>
+        <v>255.03</v>
       </c>
       <c r="BA7" s="4" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>73.8</v>
       </c>
       <c r="FX7" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="FY7" s="3" t="n">
         <v>60.3</v>
@@ -6192,16 +6192,16 @@
         <v>57.6</v>
       </c>
       <c r="GC7" s="3" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="GD7" s="3" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="GE7" s="3" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="GF7" s="3" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="GG7" s="3" t="n">
         <v>41.6</v>
@@ -6385,13 +6385,13 @@
         <v>8.619999999999999</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.971</v>
+        <v>0.973</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>10.8</v>
@@ -6418,28 +6418,28 @@
         </is>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Z8" s="5" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AA8" s="5" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="AB8" s="5" t="n">
-        <v>76.7</v>
+        <v>76.8</v>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AD8" s="5" t="n">
-        <v>70.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AE8" s="5" t="n">
-        <v>61.1</v>
+        <v>61.2</v>
       </c>
       <c r="AF8" s="5" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="AG8" s="6" t="n">
         <v>56.7</v>
@@ -6448,16 +6448,16 @@
         <v>56.2</v>
       </c>
       <c r="AI8" s="7" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="AJ8" s="7" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="AK8" s="7" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="AL8" s="7" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="AM8" s="7" t="n">
         <v>40</v>
@@ -6469,28 +6469,28 @@
         <v>36.5</v>
       </c>
       <c r="AP8" s="8" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="AQ8" s="8" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="AR8" s="8" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="AS8" s="8" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="AT8" s="8" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="AU8" s="8" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="AV8" s="8" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="AW8" s="8" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="AX8" s="8" t="n">
         <v>26</v>
@@ -6499,7 +6499,7 @@
         <v>26</v>
       </c>
       <c r="AZ8" s="3" t="n">
-        <v>246.95</v>
+        <v>246.97</v>
       </c>
       <c r="BA8" s="4" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="BB8" s="9" t="inlineStr">
         <is>
-          <t>MORE 6.0 | 60.6% | Edge +3.8</t>
+          <t>MORE 6.0 | 60.7% | Edge +3.8</t>
         </is>
       </c>
       <c r="BC8" s="4" t="inlineStr">
@@ -6520,13 +6520,13 @@
         <v>6</v>
       </c>
       <c r="BE8" s="3" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="BF8" s="3" t="n">
         <v>3.78</v>
       </c>
       <c r="BG8" s="3" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="BH8" s="4" t="inlineStr">
         <is>
@@ -6871,13 +6871,13 @@
         <v>8.619999999999999</v>
       </c>
       <c r="FL8" s="3" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="FM8" s="3" t="n">
-        <v>15.82</v>
+        <v>15.83</v>
       </c>
       <c r="FN8" s="3" t="n">
-        <v>21.64</v>
+        <v>21.67</v>
       </c>
       <c r="FO8" s="3" t="n">
         <v>4.62</v>
@@ -6896,28 +6896,28 @@
         </is>
       </c>
       <c r="FS8" s="3" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="FT8" s="3" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="FU8" s="3" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
       <c r="FV8" s="3" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
       <c r="FW8" s="3" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="FX8" s="3" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="FY8" s="3" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="FZ8" s="3" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="GA8" s="3" t="n">
         <v>53.2</v>
@@ -6926,16 +6926,16 @@
         <v>53.2</v>
       </c>
       <c r="GC8" s="3" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="GD8" s="3" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="GE8" s="3" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="GF8" s="3" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="GG8" s="3" t="n">
         <v>40</v>
@@ -6947,28 +6947,28 @@
         <v>36.5</v>
       </c>
       <c r="GJ8" s="3" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="GK8" s="3" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="GL8" s="3" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="GM8" s="3" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="GN8" s="3" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="GO8" s="3" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="GP8" s="3" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="GQ8" s="3" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="GR8" s="3" t="n">
         <v>26</v>
@@ -7104,10 +7104,10 @@
         <v>10.45</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8.73</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>8.73</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>6.62</v>
@@ -7224,16 +7224,16 @@
         <v>25.9</v>
       </c>
       <c r="AW9" s="8" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AX9" s="8" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AY9" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="AZ9" s="3" t="n">
-        <v>242.31</v>
+        <v>242.17</v>
       </c>
       <c r="BA9" s="4" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>58.7</v>
       </c>
       <c r="BF9" s="3" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BG9" s="3" t="n">
         <v>17.4</v>
@@ -7710,10 +7710,10 @@
         <v>25.9</v>
       </c>
       <c r="GQ9" s="3" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="GR9" s="3" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="GS9" s="3" t="n">
         <v>20.5</v>
@@ -8098,16 +8098,16 @@
         <v>1.03</v>
       </c>
       <c r="CI10" s="3" t="n">
-        <v>89.3</v>
+        <v>82.3</v>
       </c>
       <c r="CJ10" s="3" t="n">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="CK10" s="3" t="n">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="CL10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM10" s="4" t="inlineStr">
         <is>
@@ -8840,16 +8840,16 @@
         <v>1.03</v>
       </c>
       <c r="CI11" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="CJ11" s="3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="CK11" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="CL11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM11" s="4" t="inlineStr">
         <is>
@@ -9330,13 +9330,13 @@
         <v>9.67</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>9.220000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>9.220000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>8.199999999999999</v>
@@ -9345,13 +9345,13 @@
         <v>7.45</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>7.65</v>
+        <v>7.69</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>7.45</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.974</v>
+        <v>0.969</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>7.6</v>
@@ -9378,88 +9378,88 @@
         </is>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="Z12" s="5" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AA12" s="5" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="AB12" s="5" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>76.3</v>
+        <v>76.5</v>
       </c>
       <c r="AD12" s="5" t="n">
-        <v>75.3</v>
+        <v>75.5</v>
       </c>
       <c r="AE12" s="5" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="AF12" s="5" t="n">
-        <v>64.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="AG12" s="5" t="n">
-        <v>60.7</v>
+        <v>60.9</v>
       </c>
       <c r="AH12" s="5" t="n">
-        <v>60.2</v>
+        <v>60.4</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
       <c r="AJ12" s="7" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="AK12" s="7" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="AL12" s="7" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="AM12" s="8" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="AN12" s="8" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="AO12" s="8" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="AP12" s="8" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="AQ12" s="8" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="AR12" s="8" t="n">
-        <v>27.1</v>
+        <v>27.4</v>
       </c>
       <c r="AS12" s="8" t="n">
-        <v>27.1</v>
+        <v>27.4</v>
       </c>
       <c r="AT12" s="8" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="AU12" s="8" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="AV12" s="8" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AW12" s="8" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AX12" s="8" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AY12" s="8" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AZ12" s="3" t="n">
-        <v>233.15</v>
+        <v>233.94</v>
       </c>
       <c r="BA12" s="4" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="BB12" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.0 | 60.2% | Edge +2.2</t>
+          <t>MORE 7.0 | 60.4% | Edge +2.3</t>
         </is>
       </c>
       <c r="BC12" s="4" t="inlineStr">
@@ -9480,13 +9480,13 @@
         <v>7</v>
       </c>
       <c r="BE12" s="3" t="n">
-        <v>60.2</v>
+        <v>60.4</v>
       </c>
       <c r="BF12" s="3" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="BG12" s="3" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="BH12" s="4" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>10.15</v>
       </c>
       <c r="EA12" s="3" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="EB12" s="3" t="n">
         <v>8.6</v>
@@ -9777,10 +9777,10 @@
         <v>1</v>
       </c>
       <c r="ER12" s="3" t="n">
-        <v>1.0388</v>
+        <v>1.0408</v>
       </c>
       <c r="ES12" s="3" t="n">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="ET12" s="4" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>0.1554</v>
       </c>
       <c r="EV12" s="3" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0633</v>
       </c>
       <c r="EW12" s="3" t="n">
         <v>0.0037</v>
@@ -9839,13 +9839,13 @@
         <v>7.45</v>
       </c>
       <c r="FL12" s="3" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="FM12" s="3" t="n">
-        <v>13.87</v>
+        <v>13.86</v>
       </c>
       <c r="FN12" s="3" t="n">
-        <v>19.72</v>
+        <v>19.67</v>
       </c>
       <c r="FO12" s="3" t="n">
         <v>4.81</v>
@@ -9864,91 +9864,91 @@
         </is>
       </c>
       <c r="FS12" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="FT12" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="FU12" s="3" t="n">
-        <v>74.3</v>
+        <v>74.5</v>
       </c>
       <c r="FV12" s="3" t="n">
-        <v>74.3</v>
+        <v>74.5</v>
       </c>
       <c r="FW12" s="3" t="n">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="FX12" s="3" t="n">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="FY12" s="3" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="FZ12" s="3" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="GA12" s="3" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="GB12" s="3" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="GC12" s="3" t="n">
-        <v>48.7</v>
+        <v>49</v>
       </c>
       <c r="GD12" s="3" t="n">
-        <v>48.7</v>
+        <v>49</v>
       </c>
       <c r="GE12" s="3" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="GF12" s="3" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="GG12" s="3" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="GH12" s="3" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="GI12" s="3" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="GJ12" s="3" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="GK12" s="3" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="GL12" s="3" t="n">
-        <v>27.1</v>
+        <v>27.4</v>
       </c>
       <c r="GM12" s="3" t="n">
-        <v>27.1</v>
+        <v>27.4</v>
       </c>
       <c r="GN12" s="3" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="GO12" s="3" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="GP12" s="3" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="GQ12" s="3" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="GR12" s="3" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="GS12" s="3" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="GT12" s="3" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="GU12" s="3" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="GV12" s="3" t="n">
         <v>7.5</v>
@@ -10129,10 +10129,10 @@
         <v>86.40000000000001</v>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="AD13" s="5" t="n">
         <v>72.09999999999999</v>
@@ -10615,10 +10615,10 @@
         <v>78.90000000000001</v>
       </c>
       <c r="FV13" s="3" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="FW13" s="3" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="FX13" s="3" t="n">
         <v>67.09999999999999</v>
@@ -11066,16 +11066,16 @@
         <v>1.03</v>
       </c>
       <c r="CI14" s="3" t="n">
-        <v>89.3</v>
+        <v>82.3</v>
       </c>
       <c r="CJ14" s="3" t="n">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="CK14" s="3" t="n">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="CL14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM14" s="4" t="inlineStr">
         <is>
@@ -11808,13 +11808,13 @@
         <v>1.03</v>
       </c>
       <c r="CI15" s="3" t="n">
-        <v>83.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="CJ15" s="3" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="CK15" s="3" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="CL15" s="3" t="n">
         <v>0</v>
@@ -12298,13 +12298,13 @@
         <v>9.74</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>8.74</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>8.74</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>7.18</v>
+        <v>7.19</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>8.09</v>
@@ -12313,13 +12313,13 @@
         <v>7.37</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>7.37</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.899</v>
+        <v>0.895</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>4.6</v>
@@ -12349,73 +12349,73 @@
         <v>89.59999999999999</v>
       </c>
       <c r="Z16" s="5" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AA16" s="5" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AB16" s="5" t="n">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>69</v>
+        <v>72.5</v>
       </c>
       <c r="AD16" s="5" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="AE16" s="6" t="n">
-        <v>57.6</v>
+        <v>57.9</v>
       </c>
       <c r="AF16" s="7" t="n">
-        <v>57.1</v>
+        <v>57.4</v>
       </c>
       <c r="AG16" s="7" t="n">
-        <v>53.8</v>
+        <v>54.2</v>
       </c>
       <c r="AH16" s="7" t="n">
-        <v>53.3</v>
+        <v>53.7</v>
       </c>
       <c r="AI16" s="7" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
       <c r="AJ16" s="7" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="AK16" s="8" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="AL16" s="8" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="AM16" s="8" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="AN16" s="8" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="AO16" s="8" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="AP16" s="8" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="AQ16" s="8" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="AR16" s="8" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="AS16" s="8" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="AT16" s="8" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="AU16" s="8" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AV16" s="8" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AW16" s="8" t="n">
         <v>21.2</v>
@@ -12427,7 +12427,7 @@
         <v>17.8</v>
       </c>
       <c r="AZ16" s="3" t="n">
-        <v>227.95</v>
+        <v>228.6</v>
       </c>
       <c r="BA16" s="4" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="BB16" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 68.0% | Edge +3.7</t>
+          <t>MORE 5.0 | 68.2% | Edge +3.8</t>
         </is>
       </c>
       <c r="BC16" s="4" t="inlineStr">
@@ -12448,13 +12448,13 @@
         <v>5</v>
       </c>
       <c r="BE16" s="3" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="BF16" s="3" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="BG16" s="3" t="n">
-        <v>36</v>
+        <v>36.4</v>
       </c>
       <c r="BH16" s="4" t="inlineStr">
         <is>
@@ -12807,13 +12807,13 @@
         <v>7.37</v>
       </c>
       <c r="FL16" s="3" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="FM16" s="3" t="n">
-        <v>13.47</v>
+        <v>13.45</v>
       </c>
       <c r="FN16" s="3" t="n">
-        <v>19.76</v>
+        <v>19.72</v>
       </c>
       <c r="FO16" s="3" t="n">
         <v>4.61</v>
@@ -12835,73 +12835,73 @@
         <v>82.7</v>
       </c>
       <c r="FT16" s="3" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="FU16" s="3" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="FV16" s="3" t="n">
-        <v>66.2</v>
+        <v>66.5</v>
       </c>
       <c r="FW16" s="3" t="n">
-        <v>63</v>
+        <v>66.5</v>
       </c>
       <c r="FX16" s="3" t="n">
-        <v>63</v>
+        <v>63.2</v>
       </c>
       <c r="FY16" s="3" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="FZ16" s="3" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="GA16" s="3" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
       <c r="GB16" s="3" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
       <c r="GC16" s="3" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="GD16" s="3" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="GE16" s="3" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="GF16" s="3" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="GG16" s="3" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="GH16" s="3" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="GI16" s="3" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="GJ16" s="3" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="GK16" s="3" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="GL16" s="3" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="GM16" s="3" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="GN16" s="3" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="GO16" s="3" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="GP16" s="3" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="GQ16" s="3" t="n">
         <v>21.2</v>
@@ -13118,19 +13118,19 @@
         <v>57.4</v>
       </c>
       <c r="AI17" s="7" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="AJ17" s="7" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="AK17" s="7" t="n">
         <v>41.5</v>
       </c>
       <c r="AL17" s="8" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="AM17" s="8" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="AN17" s="8" t="n">
         <v>31.7</v>
@@ -13169,7 +13169,7 @@
         <v>14.2</v>
       </c>
       <c r="AZ17" s="3" t="n">
-        <v>222.71</v>
+        <v>222.7</v>
       </c>
       <c r="BA17" s="4" t="inlineStr">
         <is>
@@ -13604,19 +13604,19 @@
         <v>54.4</v>
       </c>
       <c r="GC17" s="3" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="GD17" s="3" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="GE17" s="3" t="n">
         <v>41.5</v>
       </c>
       <c r="GF17" s="3" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="GG17" s="3" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="GH17" s="3" t="n">
         <v>31.7</v>
@@ -13869,22 +13869,22 @@
         <v>36.1</v>
       </c>
       <c r="AL18" s="8" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="AM18" s="8" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="AN18" s="8" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="AO18" s="8" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="AP18" s="8" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="AQ18" s="8" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="AR18" s="8" t="n">
         <v>24.1</v>
@@ -13908,7 +13908,7 @@
         <v>18.2</v>
       </c>
       <c r="AY18" s="8" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="AZ18" s="3" t="n">
         <v>220.9</v>
@@ -14316,7 +14316,7 @@
         </is>
       </c>
       <c r="FS18" s="3" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="FT18" s="3" t="n">
         <v>74</v>
@@ -14355,22 +14355,22 @@
         <v>36.1</v>
       </c>
       <c r="GF18" s="3" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="GG18" s="3" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="GH18" s="3" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="GI18" s="3" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="GJ18" s="3" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="GK18" s="3" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="GL18" s="3" t="n">
         <v>24.1</v>
@@ -14394,10 +14394,10 @@
         <v>18.2</v>
       </c>
       <c r="GS18" s="3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="GT18" s="3" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="GU18" s="3" t="n">
         <v>8</v>
@@ -14524,13 +14524,13 @@
         <v>9.390000000000001</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6.06</v>
@@ -14539,13 +14539,13 @@
         <v>6.04</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>7.83</v>
+        <v>7.8</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>6.04</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>4.8</v>
@@ -14572,34 +14572,34 @@
         </is>
       </c>
       <c r="Y19" s="5" t="n">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z19" s="5" t="n">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AA19" s="5" t="n">
-        <v>83</v>
+        <v>83.3</v>
       </c>
       <c r="AB19" s="5" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AD19" s="5" t="n">
-        <v>67.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AE19" s="5" t="n">
-        <v>66.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AF19" s="6" t="n">
-        <v>55.6</v>
+        <v>55.8</v>
       </c>
       <c r="AG19" s="7" t="n">
-        <v>55.1</v>
+        <v>55.3</v>
       </c>
       <c r="AH19" s="7" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="AI19" s="7" t="n">
         <v>43.9</v>
@@ -14608,22 +14608,22 @@
         <v>42.4</v>
       </c>
       <c r="AK19" s="8" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="AL19" s="8" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="AM19" s="8" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="AN19" s="8" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="AO19" s="8" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="AP19" s="8" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="AQ19" s="8" t="n">
         <v>24.6</v>
@@ -14635,13 +14635,13 @@
         <v>23.4</v>
       </c>
       <c r="AT19" s="8" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AU19" s="8" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="AV19" s="8" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="AW19" s="8" t="n">
         <v>15.1</v>
@@ -14650,10 +14650,10 @@
         <v>15.1</v>
       </c>
       <c r="AY19" s="8" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="AZ19" s="3" t="n">
-        <v>219.56</v>
+        <v>219.72</v>
       </c>
       <c r="BA19" s="4" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="BB19" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.5 | 66.6% | Edge +2.8</t>
+          <t>MORE 5.5 | 66.9% | Edge +2.8</t>
         </is>
       </c>
       <c r="BC19" s="4" t="inlineStr">
@@ -14674,13 +14674,13 @@
         <v>5.5</v>
       </c>
       <c r="BE19" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="BF19" s="3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BG19" s="3" t="n">
-        <v>33.2</v>
+        <v>33.8</v>
       </c>
       <c r="BH19" s="4" t="inlineStr">
         <is>
@@ -15033,16 +15033,16 @@
         <v>6.04</v>
       </c>
       <c r="FL19" s="3" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="FM19" s="3" t="n">
-        <v>11.16</v>
+        <v>11.17</v>
       </c>
       <c r="FN19" s="3" t="n">
-        <v>16.56</v>
+        <v>16.58</v>
       </c>
       <c r="FO19" s="3" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="FP19" s="3" t="n">
         <v>0</v>
@@ -15058,34 +15058,34 @@
         </is>
       </c>
       <c r="FS19" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="FT19" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="FU19" s="3" t="n">
-        <v>75.5</v>
+        <v>75.8</v>
       </c>
       <c r="FV19" s="3" t="n">
-        <v>75.5</v>
+        <v>75.8</v>
       </c>
       <c r="FW19" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="FX19" s="3" t="n">
-        <v>62.1</v>
+        <v>62.4</v>
       </c>
       <c r="FY19" s="3" t="n">
-        <v>62.1</v>
+        <v>62.4</v>
       </c>
       <c r="FZ19" s="3" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="GA19" s="3" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="GB19" s="3" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="GC19" s="3" t="n">
         <v>41.4</v>
@@ -15094,22 +15094,22 @@
         <v>41.4</v>
       </c>
       <c r="GE19" s="3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="GF19" s="3" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="GG19" s="3" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="GH19" s="3" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="GI19" s="3" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="GJ19" s="3" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="GK19" s="3" t="n">
         <v>24.6</v>
@@ -15121,13 +15121,13 @@
         <v>23.4</v>
       </c>
       <c r="GN19" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="GO19" s="3" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="GP19" s="3" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="GQ19" s="3" t="n">
         <v>15.1</v>
@@ -15136,7 +15136,7 @@
         <v>15.1</v>
       </c>
       <c r="GS19" s="3" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="GT19" s="3" t="n">
         <v>6.6</v>
@@ -15266,13 +15266,13 @@
         <v>9.43</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>7.81</v>
+        <v>7.82</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>7.81</v>
+        <v>7.82</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>7.58</v>
@@ -15281,13 +15281,13 @@
         <v>7.03</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>6.99</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>1.024</v>
+        <v>1.023</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>7.2</v>
@@ -15329,10 +15329,10 @@
         <v>70.2</v>
       </c>
       <c r="AD20" s="6" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
       <c r="AE20" s="7" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="AF20" s="7" t="n">
         <v>53</v>
@@ -15341,16 +15341,16 @@
         <v>52.5</v>
       </c>
       <c r="AH20" s="7" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="AI20" s="7" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="AJ20" s="8" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="AK20" s="8" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="AL20" s="8" t="n">
         <v>31.8</v>
@@ -15368,10 +15368,10 @@
         <v>27.1</v>
       </c>
       <c r="AQ20" s="8" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="AR20" s="8" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="AS20" s="8" t="n">
         <v>21.2</v>
@@ -15380,22 +15380,22 @@
         <v>21.2</v>
       </c>
       <c r="AU20" s="8" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AV20" s="8" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AW20" s="8" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="AX20" s="8" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="AY20" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="AZ20" s="3" t="n">
-        <v>214.08</v>
+        <v>214.2</v>
       </c>
       <c r="BA20" s="4" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>70.2</v>
       </c>
       <c r="BF20" s="3" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="BG20" s="3" t="n">
         <v>40.4</v>
@@ -15775,13 +15775,13 @@
         <v>6.99</v>
       </c>
       <c r="FL20" s="3" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="FM20" s="3" t="n">
         <v>11.04</v>
       </c>
       <c r="FN20" s="3" t="n">
-        <v>17.19</v>
+        <v>17.18</v>
       </c>
       <c r="FO20" s="3" t="n">
         <v>4.57</v>
@@ -15815,10 +15815,10 @@
         <v>64.2</v>
       </c>
       <c r="FX20" s="3" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="FY20" s="3" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="FZ20" s="3" t="n">
         <v>49</v>
@@ -15827,16 +15827,16 @@
         <v>49</v>
       </c>
       <c r="GB20" s="3" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="GC20" s="3" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="GD20" s="3" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="GE20" s="3" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="GF20" s="3" t="n">
         <v>31.8</v>
@@ -15854,10 +15854,10 @@
         <v>27.1</v>
       </c>
       <c r="GK20" s="3" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="GL20" s="3" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="GM20" s="3" t="n">
         <v>21.2</v>
@@ -15866,16 +15866,16 @@
         <v>21.2</v>
       </c>
       <c r="GO20" s="3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="GP20" s="3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="GQ20" s="3" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="GR20" s="3" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="GS20" s="3" t="n">
         <v>14.1</v>
@@ -16008,10 +16008,10 @@
         <v>9.279999999999999</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>8.140000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>8.140000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>7.04</v>
@@ -16023,13 +16023,13 @@
         <v>6.91</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>7.17</v>
+        <v>7.15</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>6.91</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.964</v>
+        <v>0.966</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>3.6</v>
@@ -16056,61 +16056,61 @@
         </is>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>85.8</v>
+        <v>86.2</v>
       </c>
       <c r="Z21" s="5" t="n">
-        <v>85.8</v>
+        <v>86.2</v>
       </c>
       <c r="AA21" s="5" t="n">
-        <v>76.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AB21" s="5" t="n">
-        <v>75.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="AD21" s="5" t="n">
-        <v>69.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="AE21" s="5" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="AF21" s="6" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="AG21" s="7" t="n">
-        <v>53.6</v>
+        <v>58.7</v>
+      </c>
+      <c r="AF21" s="5" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="AG21" s="6" t="n">
+        <v>53.8</v>
       </c>
       <c r="AH21" s="7" t="n">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
       <c r="AI21" s="7" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="AJ21" s="7" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="AK21" s="8" t="n">
         <v>37.4</v>
       </c>
       <c r="AL21" s="8" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="AM21" s="8" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="AN21" s="8" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="AO21" s="8" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="AP21" s="8" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="AQ21" s="8" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="AR21" s="8" t="n">
         <v>23.6</v>
@@ -16119,25 +16119,25 @@
         <v>23.6</v>
       </c>
       <c r="AT21" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AU21" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AV21" s="8" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AW21" s="8" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AX21" s="8" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AY21" s="8" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AZ21" s="3" t="n">
-        <v>210.16</v>
+        <v>210.48</v>
       </c>
       <c r="BA21" s="4" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
       </c>
       <c r="BB21" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.5 | 58.3% | Edge +2.6</t>
+          <t>MORE 6.0 | 58.2% | Edge +2.2</t>
         </is>
       </c>
       <c r="BC21" s="4" t="inlineStr">
@@ -16155,16 +16155,16 @@
         </is>
       </c>
       <c r="BD21" s="3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE21" s="3" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="BF21" s="3" t="n">
-        <v>2.64</v>
+        <v>2.16</v>
       </c>
       <c r="BG21" s="3" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="BH21" s="4" t="inlineStr">
         <is>
@@ -16509,13 +16509,13 @@
         <v>6.91</v>
       </c>
       <c r="FL21" s="3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="FM21" s="3" t="n">
-        <v>11.86</v>
+        <v>11.87</v>
       </c>
       <c r="FN21" s="3" t="n">
-        <v>18.61</v>
+        <v>17.67</v>
       </c>
       <c r="FO21" s="3" t="n">
         <v>4.59</v>
@@ -16534,61 +16534,61 @@
         </is>
       </c>
       <c r="FS21" s="3" t="n">
-        <v>77.8</v>
+        <v>78.2</v>
       </c>
       <c r="FT21" s="3" t="n">
-        <v>77.8</v>
+        <v>78.2</v>
       </c>
       <c r="FU21" s="3" t="n">
-        <v>68.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="FV21" s="3" t="n">
-        <v>68.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="FW21" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="FX21" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="FY21" s="3" t="n">
-        <v>53.8</v>
+        <v>54.2</v>
       </c>
       <c r="FZ21" s="3" t="n">
-        <v>53.8</v>
+        <v>54.2</v>
       </c>
       <c r="GA21" s="3" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="GB21" s="3" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="GC21" s="3" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="GD21" s="3" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="GE21" s="3" t="n">
         <v>37.4</v>
       </c>
       <c r="GF21" s="3" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="GG21" s="3" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="GH21" s="3" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="GI21" s="3" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="GJ21" s="3" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="GK21" s="3" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="GL21" s="3" t="n">
         <v>23.6</v>
@@ -16597,22 +16597,22 @@
         <v>23.6</v>
       </c>
       <c r="GN21" s="3" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="GO21" s="3" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="GP21" s="3" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="GQ21" s="3" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="GR21" s="3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="GS21" s="3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="GT21" s="3" t="n">
         <v>8</v>
@@ -16742,13 +16742,13 @@
         <v>9.109999999999999</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>7.78</v>
+        <v>7.79</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>7.78</v>
+        <v>7.79</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>5.18</v>
+        <v>5.19</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>7.81</v>
@@ -16757,13 +16757,13 @@
         <v>7.18</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>7.69</v>
+        <v>7.7</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>7.18</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>13.8</v>
@@ -16790,10 +16790,10 @@
         </is>
       </c>
       <c r="Y22" s="5" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="Z22" s="5" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AA22" s="5" t="n">
         <v>69.09999999999999</v>
@@ -16829,10 +16829,10 @@
         <v>34</v>
       </c>
       <c r="AL22" s="8" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="AM22" s="8" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="AN22" s="8" t="n">
         <v>27.8</v>
@@ -16847,31 +16847,31 @@
         <v>25.9</v>
       </c>
       <c r="AR22" s="8" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="AS22" s="8" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="AT22" s="8" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AU22" s="8" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AV22" s="8" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AW22" s="8" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AX22" s="8" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AY22" s="8" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="AZ22" s="3" t="n">
-        <v>210</v>
+        <v>210.14</v>
       </c>
       <c r="BA22" s="4" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>63.2</v>
       </c>
       <c r="BF22" s="3" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BG22" s="3" t="n">
         <v>26.4</v>
@@ -17192,7 +17192,7 @@
         <v>1.0333</v>
       </c>
       <c r="ES22" s="3" t="n">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="ET22" s="4" t="inlineStr">
         <is>
@@ -17251,13 +17251,13 @@
         <v>7.18</v>
       </c>
       <c r="FL22" s="3" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="FM22" s="3" t="n">
         <v>11.72</v>
       </c>
       <c r="FN22" s="3" t="n">
-        <v>18.26</v>
+        <v>18.25</v>
       </c>
       <c r="FO22" s="3" t="n">
         <v>4.51</v>
@@ -17276,10 +17276,10 @@
         </is>
       </c>
       <c r="FS22" s="3" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="FT22" s="3" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="FU22" s="3" t="n">
         <v>61.6</v>
@@ -17315,10 +17315,10 @@
         <v>34</v>
       </c>
       <c r="GF22" s="3" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="GG22" s="3" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="GH22" s="3" t="n">
         <v>27.8</v>
@@ -17333,28 +17333,28 @@
         <v>25.9</v>
       </c>
       <c r="GL22" s="3" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="GM22" s="3" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="GN22" s="3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="GO22" s="3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="GP22" s="3" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="GQ22" s="3" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="GR22" s="3" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="GS22" s="3" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="GT22" s="3" t="n">
         <v>8</v>
@@ -17484,13 +17484,13 @@
         <v>9.06</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>7.76</v>
+        <v>7.75</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.76</v>
+        <v>7.75</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>5.31</v>
+        <v>5.3</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>6.98</v>
@@ -17499,13 +17499,13 @@
         <v>6.63</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>7.47</v>
+        <v>7.45</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>6.63</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.888</v>
+        <v>0.89</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>9.6</v>
@@ -17556,19 +17556,19 @@
         <v>52.7</v>
       </c>
       <c r="AG23" s="7" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="AH23" s="7" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="AI23" s="7" t="n">
         <v>41</v>
       </c>
       <c r="AJ23" s="8" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="AK23" s="8" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="AL23" s="8" t="n">
         <v>31.2</v>
@@ -17577,19 +17577,19 @@
         <v>31.2</v>
       </c>
       <c r="AN23" s="8" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="AO23" s="8" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="AP23" s="8" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="AQ23" s="8" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="AR23" s="8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AS23" s="8" t="n">
         <v>21.4</v>
@@ -17598,10 +17598,10 @@
         <v>21.4</v>
       </c>
       <c r="AU23" s="8" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AV23" s="8" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AW23" s="8" t="n">
         <v>16.6</v>
@@ -17613,7 +17613,7 @@
         <v>13.6</v>
       </c>
       <c r="AZ23" s="3" t="n">
-        <v>207.91</v>
+        <v>207.75</v>
       </c>
       <c r="BA23" s="4" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>64.3</v>
       </c>
       <c r="BF23" s="3" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="BG23" s="3" t="n">
         <v>28.6</v>
@@ -17993,13 +17993,13 @@
         <v>6.63</v>
       </c>
       <c r="FL23" s="3" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="FM23" s="3" t="n">
-        <v>11.52</v>
+        <v>11.53</v>
       </c>
       <c r="FN23" s="3" t="n">
-        <v>17.74</v>
+        <v>17.76</v>
       </c>
       <c r="FO23" s="3" t="n">
         <v>4.37</v>
@@ -18042,19 +18042,19 @@
         <v>48.7</v>
       </c>
       <c r="GA23" s="3" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="GB23" s="3" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="GC23" s="3" t="n">
         <v>38.5</v>
       </c>
       <c r="GD23" s="3" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="GE23" s="3" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="GF23" s="3" t="n">
         <v>31.2</v>
@@ -18063,19 +18063,19 @@
         <v>31.2</v>
       </c>
       <c r="GH23" s="3" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="GI23" s="3" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="GJ23" s="3" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="GK23" s="3" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="GL23" s="3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="GM23" s="3" t="n">
         <v>21.4</v>
@@ -18084,10 +18084,10 @@
         <v>21.4</v>
       </c>
       <c r="GO23" s="3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="GP23" s="3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="GQ23" s="3" t="n">
         <v>16.6</v>
@@ -18478,16 +18478,16 @@
         <v>1.03</v>
       </c>
       <c r="CI24" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="CJ24" s="3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="CK24" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="CL24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM24" s="4" t="inlineStr">
         <is>
@@ -18968,13 +18968,13 @@
         <v>9.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>7.83</v>
+        <v>7.82</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>7.83</v>
+        <v>7.82</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>7.75</v>
@@ -18983,13 +18983,13 @@
         <v>7.14</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>7.14</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>0.902</v>
+        <v>0.904</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>11.8</v>
@@ -19061,10 +19061,10 @@
         <v>30.2</v>
       </c>
       <c r="AN25" s="8" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="AO25" s="8" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="AP25" s="8" t="n">
         <v>26.2</v>
@@ -19073,31 +19073,31 @@
         <v>26.2</v>
       </c>
       <c r="AR25" s="8" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="AS25" s="8" t="n">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="AT25" s="8" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AU25" s="8" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AV25" s="8" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AW25" s="8" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AX25" s="8" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AY25" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="AZ25" s="3" t="n">
-        <v>206.13</v>
+        <v>205.99</v>
       </c>
       <c r="BA25" s="4" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>61</v>
       </c>
       <c r="BF25" s="3" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="BG25" s="3" t="n">
         <v>22</v>
@@ -19469,13 +19469,13 @@
         <v>7.14</v>
       </c>
       <c r="FL25" s="3" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="FM25" s="3" t="n">
-        <v>11.59</v>
+        <v>11.6</v>
       </c>
       <c r="FN25" s="3" t="n">
-        <v>17.91</v>
+        <v>17.92</v>
       </c>
       <c r="FO25" s="3" t="n">
         <v>4.21</v>
@@ -19494,7 +19494,7 @@
         </is>
       </c>
       <c r="FS25" s="3" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="FT25" s="3" t="n">
         <v>70</v>
@@ -19539,10 +19539,10 @@
         <v>30.2</v>
       </c>
       <c r="GH25" s="3" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="GI25" s="3" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="GJ25" s="3" t="n">
         <v>26.2</v>
@@ -19551,31 +19551,31 @@
         <v>26.2</v>
       </c>
       <c r="GL25" s="3" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="GM25" s="3" t="n">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="GN25" s="3" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="GO25" s="3" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="GP25" s="3" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="GQ25" s="3" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="GR25" s="3" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="GS25" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="GT25" s="3" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="GU25" s="3" t="n">
         <v>8</v>
@@ -19753,19 +19753,19 @@
         <v>89.7</v>
       </c>
       <c r="Z26" s="5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="AA26" s="5" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AB26" s="5" t="n">
-        <v>72.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="AD26" s="5" t="n">
-        <v>66.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="AE26" s="6" t="n">
         <v>55.1</v>
@@ -19774,10 +19774,10 @@
         <v>54.6</v>
       </c>
       <c r="AG26" s="7" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="AH26" s="7" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="AI26" s="7" t="n">
         <v>42.3</v>
@@ -19801,7 +19801,7 @@
         <v>27.3</v>
       </c>
       <c r="AP26" s="8" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="AQ26" s="8" t="n">
         <v>21.9</v>
@@ -19816,7 +19816,7 @@
         <v>20.2</v>
       </c>
       <c r="AU26" s="8" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="AV26" s="8" t="n">
         <v>15.7</v>
@@ -19825,13 +19825,13 @@
         <v>15.7</v>
       </c>
       <c r="AX26" s="8" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="AY26" s="8" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="AZ26" s="3" t="n">
-        <v>205.29</v>
+        <v>205.27</v>
       </c>
       <c r="BA26" s="4" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
       </c>
       <c r="BB26" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 66.6% | Edge +2.8</t>
+          <t>MORE 5.0 | 66.5% | Edge +2.8</t>
         </is>
       </c>
       <c r="BC26" s="4" t="inlineStr">
@@ -19852,13 +19852,13 @@
         <v>5</v>
       </c>
       <c r="BE26" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="BF26" s="3" t="n">
         <v>2.84</v>
       </c>
       <c r="BG26" s="3" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="BH26" s="4" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>3.7</v>
       </c>
       <c r="FM26" s="3" t="n">
-        <v>11.4</v>
+        <v>10.54</v>
       </c>
       <c r="FN26" s="3" t="n">
         <v>17.38</v>
@@ -20239,19 +20239,19 @@
         <v>82.8</v>
       </c>
       <c r="FT26" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="FU26" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="FV26" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="FW26" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="FX26" s="3" t="n">
-        <v>61.6</v>
+        <v>61.5</v>
       </c>
       <c r="FY26" s="3" t="n">
         <v>50.6</v>
@@ -20260,10 +20260,10 @@
         <v>50.6</v>
       </c>
       <c r="GA26" s="3" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="GB26" s="3" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="GC26" s="3" t="n">
         <v>39.8</v>
@@ -20287,7 +20287,7 @@
         <v>27.3</v>
       </c>
       <c r="GJ26" s="3" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="GK26" s="3" t="n">
         <v>21.9</v>
@@ -20302,7 +20302,7 @@
         <v>20.2</v>
       </c>
       <c r="GO26" s="3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="GP26" s="3" t="n">
         <v>15.7</v>
@@ -20311,10 +20311,10 @@
         <v>15.7</v>
       </c>
       <c r="GR26" s="3" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="GS26" s="3" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="GT26" s="3" t="n">
         <v>6.9</v>
@@ -20412,22 +20412,22 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHC</t>
+          <t>CIN @ COL</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -20437,143 +20437,143 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>8.449999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.63</v>
+        <v>7.34</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>7.63</v>
+        <v>7.34</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>5.48</v>
+        <v>4.95</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>6.2</v>
+        <v>7.94</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>6.12</v>
+        <v>7.27</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>7.49</v>
+        <v>7.18</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>6.12</v>
+        <v>7.25</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.8169999999999999</v>
+        <v>1.012</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>11</v>
+        <v>14.2</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>8.73</v>
+        <v>9.93</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>2|23|5|19|6</t>
+          <t>5|13|24|0|29</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>2|23|5|19|6|2|16|3|5|7</t>
+          <t>5|13|24|0|29|2|0|15|17|3</t>
         </is>
       </c>
       <c r="X27" s="4" t="inlineStr">
         <is>
-          <t>2|23|5|19|6|2|16|3|5|7|7|14|7|0|15</t>
+          <t>5|13|24|0|29|2|0|15|17|3|6|10|16|7|2</t>
         </is>
       </c>
       <c r="Y27" s="5" t="n">
-        <v>88.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Z27" s="5" t="n">
-        <v>88.2</v>
+        <v>70.3</v>
       </c>
       <c r="AA27" s="5" t="n">
-        <v>79.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="AB27" s="5" t="n">
-        <v>69.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="AD27" s="5" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="AE27" s="6" t="n">
-        <v>52.3</v>
+        <v>63.3</v>
+      </c>
+      <c r="AD27" s="6" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AE27" s="7" t="n">
+        <v>51.4</v>
       </c>
       <c r="AF27" s="7" t="n">
-        <v>51.8</v>
+        <v>47.6</v>
       </c>
       <c r="AG27" s="7" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="AH27" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI27" s="7" t="n">
-        <v>40.5</v>
+        <v>47.1</v>
+      </c>
+      <c r="AH27" s="8" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="AI27" s="8" t="n">
+        <v>38.8</v>
       </c>
       <c r="AJ27" s="8" t="n">
-        <v>35.3</v>
+        <v>33.2</v>
       </c>
       <c r="AK27" s="8" t="n">
-        <v>34.3</v>
+        <v>32.2</v>
       </c>
       <c r="AL27" s="8" t="n">
-        <v>30.7</v>
+        <v>28.6</v>
       </c>
       <c r="AM27" s="8" t="n">
-        <v>30.7</v>
+        <v>28.6</v>
       </c>
       <c r="AN27" s="8" t="n">
-        <v>27.1</v>
+        <v>28.6</v>
       </c>
       <c r="AO27" s="8" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="AP27" s="8" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="AQ27" s="8" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="AR27" s="8" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="AS27" s="8" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="AT27" s="8" t="n">
-        <v>17</v>
+        <v>20.7</v>
       </c>
       <c r="AU27" s="8" t="n">
-        <v>17</v>
+        <v>19.3</v>
       </c>
       <c r="AV27" s="8" t="n">
-        <v>16.2</v>
+        <v>19.3</v>
       </c>
       <c r="AW27" s="8" t="n">
-        <v>13.5</v>
+        <v>15.4</v>
       </c>
       <c r="AX27" s="8" t="n">
-        <v>13.5</v>
+        <v>15.4</v>
       </c>
       <c r="AY27" s="8" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ27" s="3" t="n">
-        <v>204.09</v>
+        <v>204.91</v>
       </c>
       <c r="BA27" s="4" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="BB27" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 62.7% | Edge +2.6</t>
+          <t>MORE 4.5 | 63.3% | Edge +2.8</t>
         </is>
       </c>
       <c r="BC27" s="4" t="inlineStr">
@@ -20591,16 +20591,16 @@
         </is>
       </c>
       <c r="BD27" s="3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BE27" s="3" t="n">
-        <v>62.7</v>
+        <v>63.3</v>
       </c>
       <c r="BF27" s="3" t="n">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="BG27" s="3" t="n">
-        <v>25.4</v>
+        <v>26.6</v>
       </c>
       <c r="BH27" s="4" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         </is>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BJ27" s="4" t="inlineStr">
         <is>
@@ -20617,24 +20617,24 @@
       </c>
       <c r="BK27" s="4" t="n"/>
       <c r="BL27" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BM27" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN27" s="4" t="inlineStr">
         <is>
-          <t>5-5-5-5-5-4-5</t>
+          <t>1-1-1-1-1-1-1</t>
         </is>
       </c>
       <c r="BO27" s="3" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="BP27" s="3" t="n">
         <v>97</v>
       </c>
       <c r="BQ27" s="3" t="n">
-        <v>4.52</v>
+        <v>5.04</v>
       </c>
       <c r="BR27" s="4" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
       </c>
       <c r="BU27" s="4" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="BV27" s="4" t="inlineStr">
@@ -20658,124 +20658,124 @@
         </is>
       </c>
       <c r="BW27" s="3" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="BX27" s="3" t="n">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="BY27" s="3" t="n">
-        <v>0.2422</v>
+        <v>0.1714</v>
       </c>
       <c r="BZ27" s="3" t="n">
-        <v>0.0336</v>
+        <v>0</v>
       </c>
       <c r="CA27" s="3" t="n">
-        <v>0.0863</v>
+        <v>0.0857</v>
       </c>
       <c r="CB27" s="3" t="n">
-        <v>4.33</v>
+        <v>5.44</v>
       </c>
       <c r="CC27" s="3" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="CD27" s="3" t="n">
-        <v>0.221</v>
+        <v>0.2549</v>
       </c>
       <c r="CE27" s="3" t="n">
-        <v>0.0412</v>
+        <v>0.0343</v>
       </c>
       <c r="CF27" s="4" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="CG27" s="3" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="CH27" s="3" t="n">
-        <v>1</v>
+        <v>1.055</v>
       </c>
       <c r="CI27" s="3" t="n">
-        <v>79.5</v>
+        <v>92.2</v>
       </c>
       <c r="CJ27" s="3" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="CK27" s="3" t="n">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="CL27" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CM27" s="4" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="CN27" s="3" t="n">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="CO27" s="3" t="n">
-        <v>228</v>
+        <v>303</v>
       </c>
       <c r="CP27" s="3" t="n">
-        <v>0.219</v>
+        <v>0.274</v>
       </c>
       <c r="CQ27" s="3" t="n">
-        <v>0.297</v>
+        <v>0.347</v>
       </c>
       <c r="CR27" s="3" t="n">
-        <v>0.399</v>
+        <v>0.492</v>
       </c>
       <c r="CS27" s="3" t="n">
-        <v>0.696</v>
+        <v>0.839</v>
       </c>
       <c r="CT27" s="3" t="n">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="CU27" s="3" t="n">
-        <v>0.697</v>
+        <v>0.745</v>
       </c>
       <c r="CV27" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="CW27" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="CX27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY27" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ27" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="CW27" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="CX27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY27" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="CZ27" s="3" t="n">
-        <v>30</v>
-      </c>
       <c r="DA27" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="DB27" s="3" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="DC27" s="3" t="n">
         <v>2</v>
       </c>
       <c r="DD27" s="3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="DE27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Los Angeles Angels: 2 FS|2026-07-11 vs Los Angeles Angels: 23 FS|2026-07-10 vs Los Angeles Angels: 5 FS|2026-07-09 vs Cleveland Guardians: 19 FS|2026-07-08 vs Cleveland Guardians: 6 FS</t>
+          <t>2026-07-12 vs Chicago Cubs: 5 FS|2026-07-11 vs Chicago Cubs: 13 FS|2026-07-10 vs Chicago Cubs: 24 FS|2026-07-09 vs Philadelphia Phillies: 0 FS|2026-07-08 vs Philadelphia Phillies: 29 FS</t>
         </is>
       </c>
       <c r="DF27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Los Angeles Angels: 2 FS|2026-07-11 vs Los Angeles Angels: 23 FS|2026-07-10 vs Los Angeles Angels: 5 FS|2026-07-09 vs Cleveland Guardians: 19 FS|2026-07-08 vs Cleveland Guardians: 6 FS|2026-07-07 vs Cleveland Guardians: 2 FS|2026-07-05 @ New York Yankees: 16 FS|2026-07-04 @ New York Yankees: 3 FS|2026-07-03 @ New York Yankees: 5 FS|2026-07-01 @ Houston Astros: 7 FS</t>
+          <t>2026-07-12 vs Chicago Cubs: 5 FS|2026-07-11 vs Chicago Cubs: 13 FS|2026-07-10 vs Chicago Cubs: 24 FS|2026-07-09 vs Philadelphia Phillies: 0 FS|2026-07-08 vs Philadelphia Phillies: 29 FS|2026-07-07 vs Philadelphia Phillies: 2 FS|2026-07-05 vs Baltimore Orioles: 0 FS|2026-07-04 vs Baltimore Orioles: 15 FS|2026-07-03 vs Baltimore Orioles: 17 FS|2026-07-02 @ Milwaukee Brewers: 3 FS</t>
         </is>
       </c>
       <c r="DG27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Los Angeles Angels: 2 FS|2026-07-11 vs Los Angeles Angels: 23 FS|2026-07-10 vs Los Angeles Angels: 5 FS|2026-07-09 vs Cleveland Guardians: 19 FS|2026-07-08 vs Cleveland Guardians: 6 FS|2026-07-07 vs Cleveland Guardians: 2 FS|2026-07-05 @ New York Yankees: 16 FS|2026-07-04 @ New York Yankees: 3 FS|2026-07-03 @ New York Yankees: 5 FS|2026-07-01 @ Houston Astros: 7 FS|2026-06-30 @ Houston Astros: 7 FS|2026-06-29 @ Houston Astros: 14 FS|2026-06-28 vs Colorado Rockies: 7 FS|2026-06-27 vs Colorado Rockies: 0 FS|2026-06-26 vs Colorado Rockies: 15 FS</t>
+          <t>2026-07-12 vs Chicago Cubs: 5 FS|2026-07-11 vs Chicago Cubs: 13 FS|2026-07-10 vs Chicago Cubs: 24 FS|2026-07-09 vs Philadelphia Phillies: 0 FS|2026-07-08 vs Philadelphia Phillies: 29 FS|2026-07-07 vs Philadelphia Phillies: 2 FS|2026-07-05 vs Baltimore Orioles: 0 FS|2026-07-04 vs Baltimore Orioles: 15 FS|2026-07-03 vs Baltimore Orioles: 17 FS|2026-07-02 @ Milwaukee Brewers: 3 FS|2026-07-01 @ Milwaukee Brewers: 6 FS|2026-06-30 @ Milwaukee Brewers: 10 FS|2026-06-29 @ Milwaukee Brewers: 16 FS|2026-06-28 @ Pittsburgh Pirates: 7 FS|2026-06-27 @ Pittsburgh Pirates: 2 FS</t>
         </is>
       </c>
       <c r="DH27" s="3" t="n">
@@ -20785,10 +20785,10 @@
         <v>30</v>
       </c>
       <c r="DJ27" s="3" t="n">
-        <v>8.93</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DK27" s="3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="DL27" s="4" t="inlineStr">
         <is>
@@ -20799,10 +20799,10 @@
         <v>10.43</v>
       </c>
       <c r="DN27" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="DO27" s="3" t="n">
-        <v>0.226</v>
+        <v>0.298</v>
       </c>
       <c r="DP27" s="4" t="inlineStr">
         <is>
@@ -20810,40 +20810,40 @@
         </is>
       </c>
       <c r="DQ27" s="3" t="n">
-        <v>8.93</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DR27" s="3" t="n">
-        <v>1.966</v>
+        <v>2.262</v>
       </c>
       <c r="DS27" s="3" t="n">
-        <v>0.2034</v>
+        <v>0.2615</v>
       </c>
       <c r="DT27" s="3" t="n">
-        <v>0.1186</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="DU27" s="3" t="n">
-        <v>0.0508</v>
+        <v>0.0462</v>
       </c>
       <c r="DV27" s="3" t="n">
-        <v>0.1017</v>
+        <v>0.1231</v>
       </c>
       <c r="DW27" s="3" t="n">
-        <v>0.0169</v>
+        <v>0.0615</v>
       </c>
       <c r="DX27" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DY27" s="3" t="n">
-        <v>9.17</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ27" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="EA27" s="3" t="n">
-        <v>9.08</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="EB27" s="3" t="n">
-        <v>7.51</v>
+        <v>7.47</v>
       </c>
       <c r="EC27" s="3" t="n">
         <v>28</v>
@@ -20861,25 +20861,25 @@
         <v>20</v>
       </c>
       <c r="EH27" s="3" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="EI27" s="3" t="n">
-        <v>83.61</v>
+        <v>84.67</v>
       </c>
       <c r="EJ27" s="3" t="n">
-        <v>25.29</v>
+        <v>30.34</v>
       </c>
       <c r="EK27" s="3" t="n">
-        <v>1.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="EL27" s="3" t="n">
-        <v>28.82</v>
+        <v>30.34</v>
       </c>
       <c r="EM27" s="3" t="n">
-        <v>0.39</v>
+        <v>0.442</v>
       </c>
       <c r="EN27" s="3" t="n">
-        <v>0.9298</v>
+        <v>0.9879</v>
       </c>
       <c r="EO27" s="3" t="n">
         <v>1</v>
@@ -20891,10 +20891,10 @@
         <v>1</v>
       </c>
       <c r="ER27" s="3" t="n">
-        <v>0.9839</v>
+        <v>1.0206</v>
       </c>
       <c r="ES27" s="3" t="n">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="ET27" s="4" t="inlineStr">
         <is>
@@ -20902,43 +20902,43 @@
         </is>
       </c>
       <c r="EU27" s="3" t="n">
-        <v>0.1308</v>
+        <v>0.122</v>
       </c>
       <c r="EV27" s="3" t="n">
-        <v>0.0489</v>
+        <v>0.0457</v>
       </c>
       <c r="EW27" s="3" t="n">
-        <v>0.0031</v>
+        <v>0.0065</v>
       </c>
       <c r="EX27" s="3" t="n">
-        <v>0.0427</v>
+        <v>0.035</v>
       </c>
       <c r="EY27" s="3" t="n">
-        <v>0.0898</v>
+        <v>0.0956</v>
       </c>
       <c r="EZ27" s="3" t="n">
         <v>0.008699999999999999</v>
       </c>
       <c r="FA27" s="3" t="n">
-        <v>0.2364</v>
+        <v>0.2569</v>
       </c>
       <c r="FB27" s="3" t="n">
-        <v>0.3293</v>
+        <v>0.4658</v>
       </c>
       <c r="FC27" s="3" t="n">
-        <v>0.3902</v>
+        <v>0.2876</v>
       </c>
       <c r="FD27" s="3" t="n">
-        <v>0.2805</v>
+        <v>0.2465</v>
       </c>
       <c r="FE27" s="3" t="n">
-        <v>0.1222</v>
+        <v>0.129</v>
       </c>
       <c r="FF27" s="3" t="n">
-        <v>0.1347</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="FG27" s="3" t="n">
-        <v>0.0138</v>
+        <v>0.0208</v>
       </c>
       <c r="FH27" s="3" t="n">
         <v>1</v>
@@ -20950,19 +20950,19 @@
       </c>
       <c r="FJ27" s="4" t="n"/>
       <c r="FK27" s="3" t="n">
-        <v>6.12</v>
+        <v>7.25</v>
       </c>
       <c r="FL27" s="3" t="n">
-        <v>3.03</v>
+        <v>1.92</v>
       </c>
       <c r="FM27" s="3" t="n">
-        <v>11.2</v>
+        <v>11.02</v>
       </c>
       <c r="FN27" s="3" t="n">
-        <v>16.1</v>
+        <v>18.11</v>
       </c>
       <c r="FO27" s="3" t="n">
-        <v>4.36</v>
+        <v>4.7</v>
       </c>
       <c r="FP27" s="3" t="n">
         <v>0</v>
@@ -20978,91 +20978,91 @@
         </is>
       </c>
       <c r="FS27" s="3" t="n">
-        <v>80.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="FT27" s="3" t="n">
-        <v>80.3</v>
+        <v>62.3</v>
       </c>
       <c r="FU27" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="FV27" s="3" t="n">
-        <v>62.1</v>
+        <v>57.3</v>
       </c>
       <c r="FW27" s="3" t="n">
-        <v>62.1</v>
+        <v>57.3</v>
       </c>
       <c r="FX27" s="3" t="n">
-        <v>57.7</v>
+        <v>46.9</v>
       </c>
       <c r="FY27" s="3" t="n">
-        <v>47.8</v>
+        <v>46.9</v>
       </c>
       <c r="FZ27" s="3" t="n">
-        <v>47.8</v>
+        <v>43.6</v>
       </c>
       <c r="GA27" s="3" t="n">
-        <v>45</v>
+        <v>43.6</v>
       </c>
       <c r="GB27" s="3" t="n">
-        <v>45</v>
+        <v>36.3</v>
       </c>
       <c r="GC27" s="3" t="n">
-        <v>38</v>
+        <v>36.3</v>
       </c>
       <c r="GD27" s="3" t="n">
-        <v>34.3</v>
+        <v>32.2</v>
       </c>
       <c r="GE27" s="3" t="n">
-        <v>34.3</v>
+        <v>32.2</v>
       </c>
       <c r="GF27" s="3" t="n">
-        <v>30.7</v>
+        <v>28.6</v>
       </c>
       <c r="GG27" s="3" t="n">
-        <v>30.7</v>
+        <v>28.6</v>
       </c>
       <c r="GH27" s="3" t="n">
-        <v>27.1</v>
+        <v>28.6</v>
       </c>
       <c r="GI27" s="3" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="GJ27" s="3" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="GK27" s="3" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="GL27" s="3" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="GM27" s="3" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="GN27" s="3" t="n">
-        <v>17</v>
+        <v>20.7</v>
       </c>
       <c r="GO27" s="3" t="n">
-        <v>17</v>
+        <v>19.3</v>
       </c>
       <c r="GP27" s="3" t="n">
-        <v>16.2</v>
+        <v>19.3</v>
       </c>
       <c r="GQ27" s="3" t="n">
-        <v>13.5</v>
+        <v>15.4</v>
       </c>
       <c r="GR27" s="3" t="n">
-        <v>13.5</v>
+        <v>15.4</v>
       </c>
       <c r="GS27" s="3" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="GT27" s="3" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="GU27" s="3" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="GV27" s="3" t="n">
         <v>7.5</v>
@@ -21154,22 +21154,22 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>CIN @ COL</t>
+          <t>MIN @ CHC</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -21179,143 +21179,143 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>7.27</v>
+        <v>7.68</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>7.27</v>
+        <v>7.68</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>4.93</v>
+        <v>5.49</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>7.94</v>
+        <v>6.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>7.27</v>
+        <v>6.12</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>7.15</v>
+        <v>7.51</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>7.24</v>
+        <v>6.12</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>1.017</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>14.2</v>
+        <v>11</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>10.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>9.93</v>
+        <v>8.73</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>5|13|24|0|29</t>
+          <t>2|23|5|19|6</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>5|13|24|0|29|2|0|15|17|3</t>
+          <t>2|23|5|19|6|2|16|3|5|7</t>
         </is>
       </c>
       <c r="X28" s="4" t="inlineStr">
         <is>
-          <t>5|13|24|0|29|2|0|15|17|3|6|10|16|7|2</t>
+          <t>2|23|5|19|6|2|16|3|5|7|7|14|7|0|15</t>
         </is>
       </c>
       <c r="Y28" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Z28" s="5" t="n">
-        <v>69.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AA28" s="5" t="n">
-        <v>69.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AB28" s="5" t="n">
-        <v>63.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="AD28" s="6" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="AE28" s="7" t="n">
-        <v>50.9</v>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AD28" s="5" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="AE28" s="6" t="n">
+        <v>52.6</v>
       </c>
       <c r="AF28" s="7" t="n">
-        <v>47.2</v>
+        <v>52.1</v>
       </c>
       <c r="AG28" s="7" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="AH28" s="8" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="AI28" s="8" t="n">
-        <v>38.2</v>
+        <v>48.8</v>
+      </c>
+      <c r="AH28" s="7" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="AI28" s="7" t="n">
+        <v>40.6</v>
       </c>
       <c r="AJ28" s="8" t="n">
-        <v>32.8</v>
+        <v>35.4</v>
       </c>
       <c r="AK28" s="8" t="n">
-        <v>31.8</v>
+        <v>34.4</v>
       </c>
       <c r="AL28" s="8" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="AM28" s="8" t="n">
-        <v>28.2</v>
+        <v>30.9</v>
       </c>
       <c r="AN28" s="8" t="n">
-        <v>28.2</v>
+        <v>27.2</v>
       </c>
       <c r="AO28" s="8" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="AP28" s="8" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="AQ28" s="8" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="AR28" s="8" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="AS28" s="8" t="n">
-        <v>20.6</v>
+        <v>21.3</v>
       </c>
       <c r="AT28" s="8" t="n">
-        <v>20.6</v>
+        <v>17.1</v>
       </c>
       <c r="AU28" s="8" t="n">
-        <v>19.2</v>
+        <v>17.1</v>
       </c>
       <c r="AV28" s="8" t="n">
-        <v>19.2</v>
+        <v>16.3</v>
       </c>
       <c r="AW28" s="8" t="n">
-        <v>15.2</v>
+        <v>13.6</v>
       </c>
       <c r="AX28" s="8" t="n">
-        <v>15.2</v>
+        <v>13.6</v>
       </c>
       <c r="AY28" s="8" t="n">
-        <v>14.3</v>
+        <v>12.1</v>
       </c>
       <c r="AZ28" s="3" t="n">
-        <v>203.77</v>
+        <v>204.85</v>
       </c>
       <c r="BA28" s="4" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
       </c>
       <c r="BB28" s="9" t="inlineStr">
         <is>
-          <t>MORE 4.5 | 62.7% | Edge +2.8</t>
+          <t>MORE 5.0 | 63.1% | Edge +2.7</t>
         </is>
       </c>
       <c r="BC28" s="4" t="inlineStr">
@@ -21333,16 +21333,16 @@
         </is>
       </c>
       <c r="BD28" s="3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BE28" s="3" t="n">
-        <v>62.7</v>
+        <v>63.1</v>
       </c>
       <c r="BF28" s="3" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="BG28" s="3" t="n">
-        <v>25.4</v>
+        <v>26.2</v>
       </c>
       <c r="BH28" s="4" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         </is>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ28" s="4" t="inlineStr">
         <is>
@@ -21359,24 +21359,24 @@
       </c>
       <c r="BK28" s="4" t="n"/>
       <c r="BL28" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BM28" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN28" s="4" t="inlineStr">
         <is>
-          <t>1-1-1-1-1-1-1</t>
+          <t>5-5-5-5-5-4-5</t>
         </is>
       </c>
       <c r="BO28" s="3" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="BP28" s="3" t="n">
         <v>97</v>
       </c>
       <c r="BQ28" s="3" t="n">
-        <v>5.04</v>
+        <v>4.52</v>
       </c>
       <c r="BR28" s="4" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
       </c>
       <c r="BU28" s="4" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="BV28" s="4" t="inlineStr">
@@ -21400,124 +21400,124 @@
         </is>
       </c>
       <c r="BW28" s="3" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="BX28" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BY28" s="3" t="n">
+        <v>0.2422</v>
+      </c>
+      <c r="BZ28" s="3" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="CA28" s="3" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="CB28" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="CC28" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CD28" s="3" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="CE28" s="3" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="CF28" s="4" t="inlineStr">
+        <is>
+          <t>Wrigley Field</t>
+        </is>
+      </c>
+      <c r="CG28" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CH28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="BY28" s="3" t="n">
-        <v>0.1714</v>
-      </c>
-      <c r="BZ28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA28" s="3" t="n">
-        <v>0.0857</v>
-      </c>
-      <c r="CB28" s="3" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="CC28" s="3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CD28" s="3" t="n">
-        <v>0.2549</v>
-      </c>
-      <c r="CE28" s="3" t="n">
-        <v>0.0343</v>
-      </c>
-      <c r="CF28" s="4" t="inlineStr">
-        <is>
-          <t>Coors Field</t>
-        </is>
-      </c>
-      <c r="CG28" s="3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="CH28" s="3" t="n">
-        <v>1.055</v>
-      </c>
       <c r="CI28" s="3" t="n">
-        <v>92.2</v>
+        <v>79.5</v>
       </c>
       <c r="CJ28" s="3" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="CK28" s="3" t="n">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="CL28" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CM28" s="4" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="CN28" s="3" t="n">
-        <v>340</v>
+        <v>256</v>
       </c>
       <c r="CO28" s="3" t="n">
-        <v>303</v>
+        <v>228</v>
       </c>
       <c r="CP28" s="3" t="n">
-        <v>0.274</v>
+        <v>0.219</v>
       </c>
       <c r="CQ28" s="3" t="n">
-        <v>0.347</v>
+        <v>0.297</v>
       </c>
       <c r="CR28" s="3" t="n">
-        <v>0.492</v>
+        <v>0.399</v>
       </c>
       <c r="CS28" s="3" t="n">
-        <v>0.839</v>
+        <v>0.696</v>
       </c>
       <c r="CT28" s="3" t="n">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="CU28" s="3" t="n">
-        <v>0.745</v>
+        <v>0.697</v>
       </c>
       <c r="CV28" s="3" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="CW28" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CX28" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CY28" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="CZ28" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DA28" s="3" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="DB28" s="3" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="DC28" s="3" t="n">
         <v>2</v>
       </c>
       <c r="DD28" s="3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="DE28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Chicago Cubs: 5 FS|2026-07-11 vs Chicago Cubs: 13 FS|2026-07-10 vs Chicago Cubs: 24 FS|2026-07-09 vs Philadelphia Phillies: 0 FS|2026-07-08 vs Philadelphia Phillies: 29 FS</t>
+          <t>2026-07-12 vs Los Angeles Angels: 2 FS|2026-07-11 vs Los Angeles Angels: 23 FS|2026-07-10 vs Los Angeles Angels: 5 FS|2026-07-09 vs Cleveland Guardians: 19 FS|2026-07-08 vs Cleveland Guardians: 6 FS</t>
         </is>
       </c>
       <c r="DF28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Chicago Cubs: 5 FS|2026-07-11 vs Chicago Cubs: 13 FS|2026-07-10 vs Chicago Cubs: 24 FS|2026-07-09 vs Philadelphia Phillies: 0 FS|2026-07-08 vs Philadelphia Phillies: 29 FS|2026-07-07 vs Philadelphia Phillies: 2 FS|2026-07-05 vs Baltimore Orioles: 0 FS|2026-07-04 vs Baltimore Orioles: 15 FS|2026-07-03 vs Baltimore Orioles: 17 FS|2026-07-02 @ Milwaukee Brewers: 3 FS</t>
+          <t>2026-07-12 vs Los Angeles Angels: 2 FS|2026-07-11 vs Los Angeles Angels: 23 FS|2026-07-10 vs Los Angeles Angels: 5 FS|2026-07-09 vs Cleveland Guardians: 19 FS|2026-07-08 vs Cleveland Guardians: 6 FS|2026-07-07 vs Cleveland Guardians: 2 FS|2026-07-05 @ New York Yankees: 16 FS|2026-07-04 @ New York Yankees: 3 FS|2026-07-03 @ New York Yankees: 5 FS|2026-07-01 @ Houston Astros: 7 FS</t>
         </is>
       </c>
       <c r="DG28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Chicago Cubs: 5 FS|2026-07-11 vs Chicago Cubs: 13 FS|2026-07-10 vs Chicago Cubs: 24 FS|2026-07-09 vs Philadelphia Phillies: 0 FS|2026-07-08 vs Philadelphia Phillies: 29 FS|2026-07-07 vs Philadelphia Phillies: 2 FS|2026-07-05 vs Baltimore Orioles: 0 FS|2026-07-04 vs Baltimore Orioles: 15 FS|2026-07-03 vs Baltimore Orioles: 17 FS|2026-07-02 @ Milwaukee Brewers: 3 FS|2026-07-01 @ Milwaukee Brewers: 6 FS|2026-06-30 @ Milwaukee Brewers: 10 FS|2026-06-29 @ Milwaukee Brewers: 16 FS|2026-06-28 @ Pittsburgh Pirates: 7 FS|2026-06-27 @ Pittsburgh Pirates: 2 FS</t>
+          <t>2026-07-12 vs Los Angeles Angels: 2 FS|2026-07-11 vs Los Angeles Angels: 23 FS|2026-07-10 vs Los Angeles Angels: 5 FS|2026-07-09 vs Cleveland Guardians: 19 FS|2026-07-08 vs Cleveland Guardians: 6 FS|2026-07-07 vs Cleveland Guardians: 2 FS|2026-07-05 @ New York Yankees: 16 FS|2026-07-04 @ New York Yankees: 3 FS|2026-07-03 @ New York Yankees: 5 FS|2026-07-01 @ Houston Astros: 7 FS|2026-06-30 @ Houston Astros: 7 FS|2026-06-29 @ Houston Astros: 14 FS|2026-06-28 vs Colorado Rockies: 7 FS|2026-06-27 vs Colorado Rockies: 0 FS|2026-06-26 vs Colorado Rockies: 15 FS</t>
         </is>
       </c>
       <c r="DH28" s="3" t="n">
@@ -21527,10 +21527,10 @@
         <v>30</v>
       </c>
       <c r="DJ28" s="3" t="n">
-        <v>8.630000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="DK28" s="3" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="DL28" s="4" t="inlineStr">
         <is>
@@ -21541,10 +21541,10 @@
         <v>10.43</v>
       </c>
       <c r="DN28" s="3" t="n">
-        <v>10.5</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DO28" s="3" t="n">
-        <v>0.298</v>
+        <v>0.226</v>
       </c>
       <c r="DP28" s="4" t="inlineStr">
         <is>
@@ -21552,40 +21552,40 @@
         </is>
       </c>
       <c r="DQ28" s="3" t="n">
-        <v>8.630000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="DR28" s="3" t="n">
-        <v>2.262</v>
+        <v>1.966</v>
       </c>
       <c r="DS28" s="3" t="n">
-        <v>0.2615</v>
+        <v>0.2034</v>
       </c>
       <c r="DT28" s="3" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1186</v>
       </c>
       <c r="DU28" s="3" t="n">
-        <v>0.0462</v>
+        <v>0.0508</v>
       </c>
       <c r="DV28" s="3" t="n">
-        <v>0.1231</v>
+        <v>0.1017</v>
       </c>
       <c r="DW28" s="3" t="n">
-        <v>0.0615</v>
+        <v>0.0169</v>
       </c>
       <c r="DX28" s="3" t="n">
-        <v>9.56</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DY28" s="3" t="n">
-        <v>8.720000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="DZ28" s="3" t="n">
-        <v>9.279999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="EA28" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="EB28" s="3" t="n">
-        <v>7.47</v>
+        <v>7.51</v>
       </c>
       <c r="EC28" s="3" t="n">
         <v>28</v>
@@ -21603,25 +21603,25 @@
         <v>20</v>
       </c>
       <c r="EH28" s="3" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="EI28" s="3" t="n">
-        <v>84.67</v>
+        <v>83.61</v>
       </c>
       <c r="EJ28" s="3" t="n">
-        <v>30.34</v>
+        <v>25.29</v>
       </c>
       <c r="EK28" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.76</v>
       </c>
       <c r="EL28" s="3" t="n">
-        <v>30.34</v>
+        <v>28.82</v>
       </c>
       <c r="EM28" s="3" t="n">
-        <v>0.442</v>
+        <v>0.39</v>
       </c>
       <c r="EN28" s="3" t="n">
-        <v>0.9879</v>
+        <v>0.9298</v>
       </c>
       <c r="EO28" s="3" t="n">
         <v>1</v>
@@ -21633,10 +21633,10 @@
         <v>1</v>
       </c>
       <c r="ER28" s="3" t="n">
-        <v>1.0206</v>
+        <v>0.9839</v>
       </c>
       <c r="ES28" s="3" t="n">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="ET28" s="4" t="inlineStr">
         <is>
@@ -21644,43 +21644,43 @@
         </is>
       </c>
       <c r="EU28" s="3" t="n">
-        <v>0.122</v>
+        <v>0.1308</v>
       </c>
       <c r="EV28" s="3" t="n">
-        <v>0.0457</v>
+        <v>0.0489</v>
       </c>
       <c r="EW28" s="3" t="n">
-        <v>0.0065</v>
+        <v>0.0031</v>
       </c>
       <c r="EX28" s="3" t="n">
-        <v>0.035</v>
+        <v>0.0427</v>
       </c>
       <c r="EY28" s="3" t="n">
-        <v>0.0956</v>
+        <v>0.0898</v>
       </c>
       <c r="EZ28" s="3" t="n">
         <v>0.008699999999999999</v>
       </c>
       <c r="FA28" s="3" t="n">
-        <v>0.2569</v>
+        <v>0.2364</v>
       </c>
       <c r="FB28" s="3" t="n">
-        <v>0.4658</v>
+        <v>0.3293</v>
       </c>
       <c r="FC28" s="3" t="n">
-        <v>0.2876</v>
+        <v>0.3902</v>
       </c>
       <c r="FD28" s="3" t="n">
-        <v>0.2465</v>
+        <v>0.2805</v>
       </c>
       <c r="FE28" s="3" t="n">
-        <v>0.129</v>
+        <v>0.1222</v>
       </c>
       <c r="FF28" s="3" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1347</v>
       </c>
       <c r="FG28" s="3" t="n">
-        <v>0.0208</v>
+        <v>0.0138</v>
       </c>
       <c r="FH28" s="3" t="n">
         <v>1</v>
@@ -21692,19 +21692,19 @@
       </c>
       <c r="FJ28" s="4" t="n"/>
       <c r="FK28" s="3" t="n">
-        <v>7.24</v>
+        <v>6.12</v>
       </c>
       <c r="FL28" s="3" t="n">
-        <v>1.88</v>
+        <v>3.05</v>
       </c>
       <c r="FM28" s="3" t="n">
-        <v>10.02</v>
+        <v>11.2</v>
       </c>
       <c r="FN28" s="3" t="n">
-        <v>18.15</v>
+        <v>16.91</v>
       </c>
       <c r="FO28" s="3" t="n">
-        <v>4.7</v>
+        <v>4.36</v>
       </c>
       <c r="FP28" s="3" t="n">
         <v>0</v>
@@ -21720,91 +21720,91 @@
         </is>
       </c>
       <c r="FS28" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="FT28" s="3" t="n">
-        <v>61.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="FU28" s="3" t="n">
-        <v>61.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="FV28" s="3" t="n">
-        <v>56.7</v>
+        <v>62.6</v>
       </c>
       <c r="FW28" s="3" t="n">
-        <v>56.7</v>
+        <v>62.6</v>
       </c>
       <c r="FX28" s="3" t="n">
-        <v>46.4</v>
+        <v>58.1</v>
       </c>
       <c r="FY28" s="3" t="n">
-        <v>46.4</v>
+        <v>48.1</v>
       </c>
       <c r="FZ28" s="3" t="n">
-        <v>43.2</v>
+        <v>48.1</v>
       </c>
       <c r="GA28" s="3" t="n">
-        <v>43.2</v>
+        <v>45.3</v>
       </c>
       <c r="GB28" s="3" t="n">
-        <v>35.7</v>
+        <v>45.3</v>
       </c>
       <c r="GC28" s="3" t="n">
-        <v>35.7</v>
+        <v>38.1</v>
       </c>
       <c r="GD28" s="3" t="n">
-        <v>31.8</v>
+        <v>34.4</v>
       </c>
       <c r="GE28" s="3" t="n">
-        <v>31.8</v>
+        <v>34.4</v>
       </c>
       <c r="GF28" s="3" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="GG28" s="3" t="n">
-        <v>28.2</v>
+        <v>30.9</v>
       </c>
       <c r="GH28" s="3" t="n">
-        <v>28.2</v>
+        <v>27.2</v>
       </c>
       <c r="GI28" s="3" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="GJ28" s="3" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="GK28" s="3" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="GL28" s="3" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="GM28" s="3" t="n">
-        <v>20.6</v>
+        <v>21.3</v>
       </c>
       <c r="GN28" s="3" t="n">
-        <v>20.6</v>
+        <v>17.1</v>
       </c>
       <c r="GO28" s="3" t="n">
-        <v>19.2</v>
+        <v>17.1</v>
       </c>
       <c r="GP28" s="3" t="n">
-        <v>19.2</v>
+        <v>16.3</v>
       </c>
       <c r="GQ28" s="3" t="n">
-        <v>15.2</v>
+        <v>13.6</v>
       </c>
       <c r="GR28" s="3" t="n">
-        <v>15.2</v>
+        <v>13.6</v>
       </c>
       <c r="GS28" s="3" t="n">
-        <v>14.3</v>
+        <v>12.1</v>
       </c>
       <c r="GT28" s="3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="GU28" s="3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="GV28" s="3" t="n">
         <v>7.5</v>
@@ -21928,13 +21928,13 @@
         <v>8.32</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.710000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8.710000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>7.37</v>
+        <v>6.56</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>6.66</v>
@@ -21943,13 +21943,13 @@
         <v>6.39</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8.17</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>6.39</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.782</v>
+        <v>0.788</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>5</v>
@@ -21976,88 +21976,88 @@
         </is>
       </c>
       <c r="Y29" s="5" t="n">
-        <v>90.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Z29" s="5" t="n">
-        <v>90.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AA29" s="5" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AB29" s="5" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AD29" s="5" t="n">
-        <v>72.2</v>
+        <v>68</v>
       </c>
       <c r="AE29" s="5" t="n">
-        <v>67.8</v>
+        <v>67.5</v>
       </c>
       <c r="AF29" s="6" t="n">
-        <v>57.2</v>
+        <v>56.9</v>
       </c>
       <c r="AG29" s="7" t="n">
-        <v>56.7</v>
+        <v>56.4</v>
       </c>
       <c r="AH29" s="7" t="n">
-        <v>53.1</v>
+        <v>52.9</v>
       </c>
       <c r="AI29" s="7" t="n">
-        <v>45.2</v>
+        <v>44.9</v>
       </c>
       <c r="AJ29" s="7" t="n">
-        <v>43.7</v>
+        <v>43.4</v>
       </c>
       <c r="AK29" s="8" t="n">
-        <v>39.3</v>
+        <v>39</v>
       </c>
       <c r="AL29" s="8" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="AM29" s="8" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="AN29" s="8" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="AO29" s="8" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="AP29" s="8" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="AQ29" s="8" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="AR29" s="8" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="AS29" s="8" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="AT29" s="8" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AU29" s="8" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AV29" s="8" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AW29" s="8" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="AX29" s="8" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="AY29" s="8" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="AZ29" s="3" t="n">
-        <v>202.65</v>
+        <v>201.71</v>
       </c>
       <c r="BA29" s="4" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BB29" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.5 | 67.8% | Edge +3.2</t>
+          <t>MORE 5.5 | 67.5% | Edge +3.2</t>
         </is>
       </c>
       <c r="BC29" s="4" t="inlineStr">
@@ -22078,13 +22078,13 @@
         <v>5.5</v>
       </c>
       <c r="BE29" s="3" t="n">
-        <v>67.8</v>
+        <v>67.5</v>
       </c>
       <c r="BF29" s="3" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="BG29" s="3" t="n">
-        <v>35.6</v>
+        <v>35</v>
       </c>
       <c r="BH29" s="4" t="inlineStr">
         <is>
@@ -22429,16 +22429,16 @@
         <v>6.39</v>
       </c>
       <c r="FL29" s="3" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="FM29" s="3" t="n">
-        <v>12.85</v>
+        <v>12.87</v>
       </c>
       <c r="FN29" s="3" t="n">
-        <v>17.54</v>
+        <v>17.6</v>
       </c>
       <c r="FO29" s="3" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="FP29" s="3" t="n">
         <v>0</v>
@@ -22454,91 +22454,91 @@
         </is>
       </c>
       <c r="FS29" s="3" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="FT29" s="3" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="FU29" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="FV29" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="FW29" s="3" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="FX29" s="3" t="n">
-        <v>67.2</v>
+        <v>63</v>
       </c>
       <c r="FY29" s="3" t="n">
-        <v>63.3</v>
+        <v>63</v>
       </c>
       <c r="FZ29" s="3" t="n">
-        <v>53.2</v>
+        <v>52.9</v>
       </c>
       <c r="GA29" s="3" t="n">
-        <v>53.2</v>
+        <v>52.9</v>
       </c>
       <c r="GB29" s="3" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
       <c r="GC29" s="3" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="GD29" s="3" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="GE29" s="3" t="n">
-        <v>39.3</v>
+        <v>39</v>
       </c>
       <c r="GF29" s="3" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="GG29" s="3" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="GH29" s="3" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="GI29" s="3" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="GJ29" s="3" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="GK29" s="3" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="GL29" s="3" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="GM29" s="3" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="GN29" s="3" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="GO29" s="3" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="GP29" s="3" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="GQ29" s="3" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="GR29" s="3" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="GS29" s="3" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="GT29" s="3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="GU29" s="3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="GV29" s="3" t="n">
         <v>7.5</v>
@@ -22662,13 +22662,13 @@
         <v>8.949999999999999</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>8.24</v>
@@ -22677,13 +22677,13 @@
         <v>7.48</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>7.38</v>
+        <v>7.27</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>7.46</v>
+        <v>7.43</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1.013</v>
+        <v>1.03</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>10.4</v>
@@ -22710,70 +22710,70 @@
         </is>
       </c>
       <c r="Y30" s="5" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z30" s="5" t="n">
-        <v>68.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="AA30" s="5" t="n">
-        <v>68.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="AB30" s="5" t="n">
-        <v>63.6</v>
+        <v>63.9</v>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>62.6</v>
+        <v>62.9</v>
       </c>
       <c r="AD30" s="6" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="AE30" s="7" t="n">
-        <v>50.6</v>
+        <v>51</v>
       </c>
       <c r="AF30" s="7" t="n">
-        <v>47</v>
+        <v>47.4</v>
       </c>
       <c r="AG30" s="7" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
       <c r="AH30" s="8" t="n">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="AI30" s="8" t="n">
-        <v>38.4</v>
+        <v>38.7</v>
       </c>
       <c r="AJ30" s="8" t="n">
-        <v>33.4</v>
+        <v>33.8</v>
       </c>
       <c r="AK30" s="8" t="n">
-        <v>32.4</v>
+        <v>32.8</v>
       </c>
       <c r="AL30" s="8" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="AM30" s="8" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="AN30" s="8" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="AO30" s="8" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="AP30" s="8" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="AQ30" s="8" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="AR30" s="8" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="AS30" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AT30" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AU30" s="8" t="n">
         <v>20.6</v>
@@ -22782,16 +22782,16 @@
         <v>20.6</v>
       </c>
       <c r="AW30" s="8" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="AX30" s="8" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="AY30" s="8" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="AZ30" s="3" t="n">
-        <v>201.33</v>
+        <v>201.04</v>
       </c>
       <c r="BA30" s="4" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="BB30" s="9" t="inlineStr">
         <is>
-          <t>MORE 4.5 | 62.6% | Edge +2.9</t>
+          <t>MORE 4.5 | 62.9% | Edge +2.9</t>
         </is>
       </c>
       <c r="BC30" s="4" t="inlineStr">
@@ -22812,13 +22812,13 @@
         <v>4.5</v>
       </c>
       <c r="BE30" s="3" t="n">
-        <v>62.6</v>
+        <v>62.9</v>
       </c>
       <c r="BF30" s="3" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="BG30" s="3" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="BH30" s="4" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>1.0226</v>
       </c>
       <c r="ES30" s="3" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="ET30" s="4" t="inlineStr">
         <is>
@@ -23168,16 +23168,16 @@
       </c>
       <c r="FJ30" s="4" t="n"/>
       <c r="FK30" s="3" t="n">
-        <v>7.46</v>
+        <v>7.43</v>
       </c>
       <c r="FL30" s="3" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="FM30" s="3" t="n">
-        <v>11.02</v>
+        <v>11.05</v>
       </c>
       <c r="FN30" s="3" t="n">
-        <v>18.12</v>
+        <v>18.26</v>
       </c>
       <c r="FO30" s="3" t="n">
         <v>4.6</v>
@@ -23196,70 +23196,70 @@
         </is>
       </c>
       <c r="FS30" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="FT30" s="3" t="n">
-        <v>60.9</v>
+        <v>61.3</v>
       </c>
       <c r="FU30" s="3" t="n">
-        <v>60.9</v>
+        <v>61.3</v>
       </c>
       <c r="FV30" s="3" t="n">
-        <v>56.6</v>
+        <v>56.9</v>
       </c>
       <c r="FW30" s="3" t="n">
-        <v>56.6</v>
+        <v>56.9</v>
       </c>
       <c r="FX30" s="3" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="FY30" s="3" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="FZ30" s="3" t="n">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="GA30" s="3" t="n">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="GB30" s="3" t="n">
-        <v>35.9</v>
+        <v>36.2</v>
       </c>
       <c r="GC30" s="3" t="n">
-        <v>35.9</v>
+        <v>36.2</v>
       </c>
       <c r="GD30" s="3" t="n">
-        <v>32.4</v>
+        <v>32.8</v>
       </c>
       <c r="GE30" s="3" t="n">
-        <v>32.4</v>
+        <v>32.8</v>
       </c>
       <c r="GF30" s="3" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="GG30" s="3" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="GH30" s="3" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="GI30" s="3" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="GJ30" s="3" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="GK30" s="3" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="GL30" s="3" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="GM30" s="3" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="GN30" s="3" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="GO30" s="3" t="n">
         <v>20.6</v>
@@ -23268,13 +23268,13 @@
         <v>20.6</v>
       </c>
       <c r="GQ30" s="3" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="GR30" s="3" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="GS30" s="3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="GT30" s="3" t="n">
         <v>8</v>
@@ -23372,22 +23372,22 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>TB @ BOS</t>
+          <t>STL @ ARI</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -23397,143 +23397,143 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>9.08</v>
+        <v>8.92</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>7.52</v>
+        <v>8</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>7.52</v>
+        <v>8</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>5.37</v>
+        <v>6.56</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>5.9</v>
+        <v>4.79</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>5.94</v>
+        <v>5.28</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>6.96</v>
+        <v>7.41</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>5.94</v>
+        <v>5.33</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0.854</v>
+        <v>0.72</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.6</v>
+        <v>5.07</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>18|17|13|8|14</t>
+          <t>6|27|0|5|0</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>18|17|13|8|14|2|0|3|5|0</t>
+          <t>6|27|0|5|0|7|0|0|0|10</t>
         </is>
       </c>
       <c r="X31" s="4" t="inlineStr">
         <is>
-          <t>18|17|13|8|14|2|0|3|5|0|3|10|14|2|20</t>
+          <t>6|27|0|5|0|7|0|0|0|10|0|8|0|8|5</t>
         </is>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>90.3</v>
+        <v>90</v>
       </c>
       <c r="Z31" s="5" t="n">
-        <v>83.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="AA31" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AB31" s="5" t="n">
-        <v>71.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>70.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="AD31" s="5" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="AE31" s="6" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="AF31" s="7" t="n">
-        <v>53.6</v>
+        <v>71.2</v>
+      </c>
+      <c r="AE31" s="5" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AF31" s="6" t="n">
+        <v>55.5</v>
       </c>
       <c r="AG31" s="7" t="n">
-        <v>49.5</v>
+        <v>55</v>
       </c>
       <c r="AH31" s="7" t="n">
-        <v>49</v>
+        <v>50.9</v>
       </c>
       <c r="AI31" s="7" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="AJ31" s="8" t="n">
-        <v>34.3</v>
+        <v>42.8</v>
+      </c>
+      <c r="AJ31" s="7" t="n">
+        <v>41.3</v>
       </c>
       <c r="AK31" s="8" t="n">
-        <v>33.3</v>
+        <v>36.1</v>
       </c>
       <c r="AL31" s="8" t="n">
-        <v>29.3</v>
+        <v>31.9</v>
       </c>
       <c r="AM31" s="8" t="n">
-        <v>29.3</v>
+        <v>28</v>
       </c>
       <c r="AN31" s="8" t="n">
-        <v>25.3</v>
+        <v>28</v>
       </c>
       <c r="AO31" s="8" t="n">
-        <v>22.9</v>
+        <v>25.8</v>
       </c>
       <c r="AP31" s="8" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AQ31" s="8" t="n">
-        <v>19.9</v>
+        <v>23</v>
       </c>
       <c r="AR31" s="8" t="n">
-        <v>19.9</v>
+        <v>21.7</v>
       </c>
       <c r="AS31" s="8" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="AT31" s="8" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="AU31" s="8" t="n">
-        <v>15.1</v>
+        <v>16.9</v>
       </c>
       <c r="AV31" s="8" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="AW31" s="8" t="n">
-        <v>14.2</v>
+        <v>12.4</v>
       </c>
       <c r="AX31" s="8" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="AY31" s="8" t="n">
-        <v>11.9</v>
+        <v>10.7</v>
       </c>
       <c r="AZ31" s="3" t="n">
-        <v>199.09</v>
+        <v>199.51</v>
       </c>
       <c r="BA31" s="4" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="BB31" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 65.8% | Edge +2.5</t>
+          <t>MORE 5.5 | 66.6% | Edge +2.5</t>
         </is>
       </c>
       <c r="BC31" s="4" t="inlineStr">
@@ -23551,24 +23551,24 @@
         </is>
       </c>
       <c r="BD31" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE31" s="3" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="BF31" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG31" s="3" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="BH31" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="BI31" s="3" t="n">
         <v>5</v>
-      </c>
-      <c r="BE31" s="3" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="BF31" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BG31" s="3" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="BH31" s="4" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="BI31" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="BJ31" s="4" t="inlineStr">
         <is>
@@ -23577,24 +23577,24 @@
       </c>
       <c r="BK31" s="4" t="n"/>
       <c r="BL31" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BM31" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BN31" s="4" t="inlineStr">
         <is>
-          <t>2-2-2-2-2-2-2</t>
+          <t>5-5-5-8-5</t>
         </is>
       </c>
       <c r="BO31" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BP31" s="3" t="n">
-        <v>97</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="BQ31" s="3" t="n">
-        <v>5.02</v>
+        <v>4.52</v>
       </c>
       <c r="BR31" s="4" t="inlineStr">
         <is>
@@ -23602,14 +23602,14 @@
         </is>
       </c>
       <c r="BS31" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BT31" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="BU31" s="4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Merrill Kelly</t>
         </is>
       </c>
       <c r="BV31" s="4" t="inlineStr">
@@ -23618,124 +23618,116 @@
         </is>
       </c>
       <c r="BW31" s="3" t="n">
-        <v>4.2</v>
+        <v>5.38</v>
       </c>
       <c r="BX31" s="3" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="BY31" s="3" t="n">
-        <v>0.224</v>
+        <v>0.2506</v>
       </c>
       <c r="BZ31" s="3" t="n">
-        <v>0.03</v>
+        <v>0.0487</v>
       </c>
       <c r="CA31" s="3" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0925</v>
       </c>
       <c r="CB31" s="3" t="n">
-        <v>3.59</v>
+        <v>4.21</v>
       </c>
       <c r="CC31" s="3" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="CD31" s="3" t="n">
-        <v>0.214</v>
+        <v>0.2245</v>
       </c>
       <c r="CE31" s="3" t="n">
-        <v>0.0276</v>
+        <v>0.0325</v>
       </c>
       <c r="CF31" s="4" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="CG31" s="3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="CH31" s="3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="CI31" s="3" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="CJ31" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="CK31" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="CL31" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="CI31" s="4" t="n"/>
+      <c r="CJ31" s="4" t="n"/>
+      <c r="CK31" s="4" t="n"/>
+      <c r="CL31" s="4" t="n"/>
       <c r="CM31" s="4" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>Indoor/retractable neutral</t>
         </is>
       </c>
       <c r="CN31" s="3" t="n">
-        <v>406</v>
+        <v>121</v>
       </c>
       <c r="CO31" s="3" t="n">
-        <v>340</v>
+        <v>104</v>
       </c>
       <c r="CP31" s="3" t="n">
-        <v>0.297</v>
+        <v>0.26</v>
       </c>
       <c r="CQ31" s="3" t="n">
-        <v>0.394</v>
+        <v>0.355</v>
       </c>
       <c r="CR31" s="3" t="n">
-        <v>0.471</v>
+        <v>0.423</v>
       </c>
       <c r="CS31" s="3" t="n">
-        <v>0.865</v>
+        <v>0.778</v>
       </c>
       <c r="CT31" s="3" t="n">
-        <v>288</v>
+        <v>93</v>
       </c>
       <c r="CU31" s="3" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="CV31" s="3" t="n">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="CW31" s="3" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="CX31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY31" s="3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="CZ31" s="3" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="DA31" s="3" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="DB31" s="3" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="DC31" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="DD31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Seattle Mariners: 18 FS|2026-07-11 vs Seattle Mariners: 17 FS|2026-07-10 vs Seattle Mariners: 13 FS|2026-07-09 vs New York Yankees: 8 FS|2026-07-08 vs New York Yankees: 14 FS</t>
+          <t>2026-07-12 vs Atlanta Braves: 6 FS|2026-07-11 vs Atlanta Braves: 27 FS|2026-07-10 vs Atlanta Braves: 0 FS|2026-07-09 vs Milwaukee Brewers: 5 FS|2026-07-08 vs Milwaukee Brewers: 0 FS</t>
         </is>
       </c>
       <c r="DF31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Seattle Mariners: 18 FS|2026-07-11 vs Seattle Mariners: 17 FS|2026-07-10 vs Seattle Mariners: 13 FS|2026-07-09 vs New York Yankees: 8 FS|2026-07-08 vs New York Yankees: 14 FS|2026-07-07 vs New York Yankees: 2 FS|2026-07-06 vs New York Yankees: 0 FS|2026-07-05 @ Houston Astros: 3 FS|2026-07-04 @ Houston Astros: 5 FS|2026-07-03 @ Houston Astros: 0 FS</t>
+          <t>2026-07-12 vs Atlanta Braves: 6 FS|2026-07-11 vs Atlanta Braves: 27 FS|2026-07-10 vs Atlanta Braves: 0 FS|2026-07-09 vs Milwaukee Brewers: 5 FS|2026-07-08 vs Milwaukee Brewers: 0 FS|2026-07-07 vs Milwaukee Brewers: 7 FS|2026-07-06 vs Milwaukee Brewers: 0 FS|2026-07-05 @ Chicago Cubs: 0 FS|2026-07-04 @ Chicago Cubs: 0 FS|2026-07-02 @ Atlanta Braves: 10 FS</t>
         </is>
       </c>
       <c r="DG31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Seattle Mariners: 18 FS|2026-07-11 vs Seattle Mariners: 17 FS|2026-07-10 vs Seattle Mariners: 13 FS|2026-07-09 vs New York Yankees: 8 FS|2026-07-08 vs New York Yankees: 14 FS|2026-07-07 vs New York Yankees: 2 FS|2026-07-06 vs New York Yankees: 0 FS|2026-07-05 @ Houston Astros: 3 FS|2026-07-04 @ Houston Astros: 5 FS|2026-07-03 @ Houston Astros: 0 FS|2026-07-02 @ Kansas City Royals: 3 FS|2026-07-01 @ Kansas City Royals: 10 FS|2026-06-30 @ Kansas City Royals: 14 FS|2026-06-28 vs Arizona Diamondbacks: 2 FS|2026-06-27 vs Arizona Diamondbacks: 20 FS</t>
+          <t>2026-07-12 vs Atlanta Braves: 6 FS|2026-07-11 vs Atlanta Braves: 27 FS|2026-07-10 vs Atlanta Braves: 0 FS|2026-07-09 vs Milwaukee Brewers: 5 FS|2026-07-08 vs Milwaukee Brewers: 0 FS|2026-07-07 vs Milwaukee Brewers: 7 FS|2026-07-06 vs Milwaukee Brewers: 0 FS|2026-07-05 @ Chicago Cubs: 0 FS|2026-07-04 @ Chicago Cubs: 0 FS|2026-07-02 @ Atlanta Braves: 10 FS|2026-07-01 @ Atlanta Braves: 0 FS|2026-06-30 @ Atlanta Braves: 8 FS|2026-06-28 vs Miami Marlins: 0 FS|2026-06-27 vs Miami Marlins: 8 FS|2026-06-26 vs Miami Marlins: 5 FS</t>
         </is>
       </c>
       <c r="DH31" s="3" t="n">
@@ -23745,10 +23737,10 @@
         <v>30</v>
       </c>
       <c r="DJ31" s="3" t="n">
-        <v>8.5</v>
+        <v>6.07</v>
       </c>
       <c r="DK31" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="DL31" s="4" t="inlineStr">
         <is>
@@ -23756,54 +23748,54 @@
         </is>
       </c>
       <c r="DM31" s="3" t="n">
-        <v>10.29</v>
+        <v>6.43</v>
       </c>
       <c r="DN31" s="3" t="n">
-        <v>7.79</v>
+        <v>5.07</v>
       </c>
       <c r="DO31" s="3" t="n">
-        <v>0.34</v>
+        <v>0.214</v>
       </c>
       <c r="DP31" s="4" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="DQ31" s="3" t="n">
-        <v>8.5</v>
+        <v>6.07</v>
       </c>
       <c r="DR31" s="3" t="n">
-        <v>1.787</v>
+        <v>1.511</v>
       </c>
       <c r="DS31" s="3" t="n">
-        <v>0.2951</v>
+        <v>0.1915</v>
       </c>
       <c r="DT31" s="3" t="n">
-        <v>0.082</v>
+        <v>0.0638</v>
       </c>
       <c r="DU31" s="3" t="n">
-        <v>0.0164</v>
+        <v>0.0213</v>
       </c>
       <c r="DV31" s="3" t="n">
-        <v>0.082</v>
+        <v>0.1064</v>
       </c>
       <c r="DW31" s="3" t="n">
-        <v>0</v>
+        <v>0.0213</v>
       </c>
       <c r="DX31" s="3" t="n">
-        <v>9.220000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DY31" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="DZ31" s="3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="EA31" s="3" t="n">
-        <v>9.34</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="EB31" s="3" t="n">
-        <v>8.94</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="EC31" s="3" t="n">
         <v>28</v>
@@ -23821,25 +23813,25 @@
         <v>20</v>
       </c>
       <c r="EH31" s="3" t="n">
-        <v>285</v>
+        <v>128</v>
       </c>
       <c r="EI31" s="3" t="n">
-        <v>85.12</v>
+        <v>86.37</v>
       </c>
       <c r="EJ31" s="3" t="n">
-        <v>25.61</v>
+        <v>34.38</v>
       </c>
       <c r="EK31" s="3" t="n">
-        <v>1.05</v>
+        <v>2.34</v>
       </c>
       <c r="EL31" s="3" t="n">
-        <v>33.68</v>
+        <v>30.47</v>
       </c>
       <c r="EM31" s="3" t="n">
-        <v>0.424</v>
+        <v>0.41</v>
       </c>
       <c r="EN31" s="3" t="n">
-        <v>0.9683</v>
+        <v>1.0092</v>
       </c>
       <c r="EO31" s="3" t="n">
         <v>1</v>
@@ -23851,54 +23843,54 @@
         <v>1</v>
       </c>
       <c r="ER31" s="3" t="n">
-        <v>1</v>
+        <v>1.0764</v>
       </c>
       <c r="ES31" s="3" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="ET31" s="4" t="inlineStr">
         <is>
-          <t>Fallback</t>
+          <t>Statcast</t>
         </is>
       </c>
       <c r="EU31" s="3" t="n">
-        <v>0.1535</v>
+        <v>0.1536</v>
       </c>
       <c r="EV31" s="3" t="n">
-        <v>0.0524</v>
+        <v>0.0559</v>
       </c>
       <c r="EW31" s="3" t="n">
-        <v>0.0026</v>
+        <v>0.005</v>
       </c>
       <c r="EX31" s="3" t="n">
-        <v>0.031</v>
+        <v>0.0415</v>
       </c>
       <c r="EY31" s="3" t="n">
-        <v>0.0961</v>
+        <v>0.1036</v>
       </c>
       <c r="EZ31" s="3" t="n">
-        <v>0.0158</v>
+        <v>0.0086</v>
       </c>
       <c r="FA31" s="3" t="n">
-        <v>0.2194</v>
+        <v>0.1932</v>
       </c>
       <c r="FB31" s="3" t="n">
-        <v>0.355</v>
+        <v>0.4675</v>
       </c>
       <c r="FC31" s="3" t="n">
-        <v>0.3261</v>
+        <v>0.2858</v>
       </c>
       <c r="FD31" s="3" t="n">
-        <v>0.3189</v>
+        <v>0.2467</v>
       </c>
       <c r="FE31" s="3" t="n">
-        <v>0.1122</v>
+        <v>0.1179</v>
       </c>
       <c r="FF31" s="3" t="n">
-        <v>0.1335</v>
+        <v>0.1261</v>
       </c>
       <c r="FG31" s="3" t="n">
-        <v>0.0077</v>
+        <v>0.0128</v>
       </c>
       <c r="FH31" s="3" t="n">
         <v>1</v>
@@ -23910,19 +23902,19 @@
       </c>
       <c r="FJ31" s="4" t="n"/>
       <c r="FK31" s="3" t="n">
-        <v>5.94</v>
+        <v>5.33</v>
       </c>
       <c r="FL31" s="3" t="n">
-        <v>3.66</v>
+        <v>4.4</v>
       </c>
       <c r="FM31" s="3" t="n">
-        <v>10.49</v>
+        <v>10.88</v>
       </c>
       <c r="FN31" s="3" t="n">
-        <v>16.47</v>
+        <v>15.92</v>
       </c>
       <c r="FO31" s="3" t="n">
-        <v>4.39</v>
+        <v>4.16</v>
       </c>
       <c r="FP31" s="3" t="n">
         <v>0</v>
@@ -23938,94 +23930,94 @@
         </is>
       </c>
       <c r="FS31" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="FT31" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="FU31" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="FV31" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="FW31" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="FX31" s="3" t="n">
-        <v>60.8</v>
+        <v>66.2</v>
       </c>
       <c r="FY31" s="3" t="n">
-        <v>49.6</v>
+        <v>62.1</v>
       </c>
       <c r="FZ31" s="3" t="n">
-        <v>49.6</v>
+        <v>51.5</v>
       </c>
       <c r="GA31" s="3" t="n">
-        <v>46</v>
+        <v>51.5</v>
       </c>
       <c r="GB31" s="3" t="n">
-        <v>46</v>
+        <v>47.9</v>
       </c>
       <c r="GC31" s="3" t="n">
-        <v>38</v>
+        <v>40.3</v>
       </c>
       <c r="GD31" s="3" t="n">
-        <v>33.3</v>
+        <v>40.3</v>
       </c>
       <c r="GE31" s="3" t="n">
-        <v>33.3</v>
+        <v>36.1</v>
       </c>
       <c r="GF31" s="3" t="n">
-        <v>29.3</v>
+        <v>31.9</v>
       </c>
       <c r="GG31" s="3" t="n">
-        <v>29.3</v>
+        <v>28</v>
       </c>
       <c r="GH31" s="3" t="n">
-        <v>25.3</v>
+        <v>28</v>
       </c>
       <c r="GI31" s="3" t="n">
-        <v>22.9</v>
+        <v>25.8</v>
       </c>
       <c r="GJ31" s="3" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="GK31" s="3" t="n">
-        <v>19.9</v>
+        <v>23</v>
       </c>
       <c r="GL31" s="3" t="n">
-        <v>19.9</v>
+        <v>21.7</v>
       </c>
       <c r="GM31" s="3" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="GN31" s="3" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="GO31" s="3" t="n">
-        <v>15.1</v>
+        <v>16.9</v>
       </c>
       <c r="GP31" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="GQ31" s="3" t="n">
-        <v>14.2</v>
+        <v>12.4</v>
       </c>
       <c r="GR31" s="3" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="GS31" s="3" t="n">
-        <v>11.9</v>
+        <v>10.7</v>
       </c>
       <c r="GT31" s="3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="GU31" s="3" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="GV31" s="3" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="GW31" s="3" t="n">
         <v>7</v>
